--- a/urunler.xlsx
+++ b/urunler.xlsx
@@ -5,19 +5,18 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\b2b\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\Githup\portal\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6E5BFDF-B831-44A7-841F-B80AC4A7B052}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A15BCA2-6627-47C5-BDDE-2EAF26AAC79D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1080" yWindow="1080" windowWidth="18870" windowHeight="9360" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="urunler" sheetId="1" r:id="rId1"/>
     <sheet name="bayiler" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>

--- a/urunler.xlsx
+++ b/urunler.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\Githup\portal\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A15BCA2-6627-47C5-BDDE-2EAF26AAC79D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E95E9C49-2932-4847-A665-8B47A1E43E3A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/urunler.xlsx
+++ b/urunler.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\Githup\portal\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E95E9C49-2932-4847-A665-8B47A1E43E3A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98578790-5887-4A73-AE19-86C838F514D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/urunler.xlsx
+++ b/urunler.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\Githup\portal\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98578790-5887-4A73-AE19-86C838F514D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD759230-3532-4FBF-A9B7-C0CD652495DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/urunler.xlsx
+++ b/urunler.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\Githup\portal\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD759230-3532-4FBF-A9B7-C0CD652495DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{362897F4-6B55-4FA0-9465-90E41B21A7F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="311" uniqueCount="240">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="311" uniqueCount="242">
   <si>
     <t>urun_no</t>
   </si>
@@ -735,9 +735,6 @@
     <t>WD-473.PNG</t>
   </si>
   <si>
-    <t>REKLAM</t>
-  </si>
-  <si>
     <t>KAMPANYA1</t>
   </si>
   <si>
@@ -754,6 +751,15 @@
   </si>
   <si>
     <t>KAMPANYA3.PNG</t>
+  </si>
+  <si>
+    <t>REKLAM1</t>
+  </si>
+  <si>
+    <t>REKLAM2</t>
+  </si>
+  <si>
+    <t>REKLAM3</t>
   </si>
 </sst>
 </file>
@@ -2430,35 +2436,35 @@
     </row>
     <row r="69" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A69" s="8" t="s">
+        <v>239</v>
+      </c>
+      <c r="B69" s="8" t="s">
         <v>233</v>
       </c>
-      <c r="B69" s="8" t="s">
-        <v>234</v>
-      </c>
       <c r="G69" s="2" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
     </row>
     <row r="70" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A70" s="8" t="s">
-        <v>233</v>
+        <v>240</v>
       </c>
       <c r="B70" s="8" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="G70" s="2" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
     </row>
     <row r="71" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A71" s="8" t="s">
-        <v>233</v>
+        <v>241</v>
       </c>
       <c r="B71" s="8" t="s">
+        <v>237</v>
+      </c>
+      <c r="G71" s="2" t="s">
         <v>238</v>
-      </c>
-      <c r="G71" s="2" t="s">
-        <v>239</v>
       </c>
     </row>
   </sheetData>

--- a/urunler.xlsx
+++ b/urunler.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\Githup\portal\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{362897F4-6B55-4FA0-9465-90E41B21A7F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8CEBC48B-A5B3-4380-B0D2-B22BF65EB277}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1295,371 +1295,362 @@
       </c>
     </row>
     <row r="12" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" t="s">
-        <v>66</v>
-      </c>
-      <c r="B12" t="s">
-        <v>75</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="D12" s="7">
-        <v>6480.92</v>
-      </c>
-      <c r="F12">
-        <v>5</v>
+      <c r="A12" s="8" t="s">
+        <v>239</v>
+      </c>
+      <c r="B12" s="8" t="s">
+        <v>233</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>89</v>
+        <v>235</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B13" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>88</v>
       </c>
       <c r="D13" s="7">
-        <v>8841.6200000000008</v>
+        <v>6480.92</v>
       </c>
       <c r="F13">
         <v>5</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B14" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>88</v>
       </c>
       <c r="D14" s="7">
-        <v>8520.89</v>
+        <v>8841.6200000000008</v>
       </c>
       <c r="F14">
         <v>5</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B15" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>88</v>
       </c>
       <c r="D15" s="7">
-        <v>9540.83</v>
+        <v>8520.89</v>
       </c>
       <c r="F15">
         <v>5</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="16" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B16" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>88</v>
       </c>
       <c r="D16" s="7">
-        <v>7620.91</v>
+        <v>9540.83</v>
       </c>
       <c r="F16">
         <v>5</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
     </row>
     <row r="17" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="B17" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>88</v>
       </c>
       <c r="D17" s="7">
-        <v>2577.54</v>
+        <v>7620.91</v>
       </c>
       <c r="F17">
         <v>5</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
     </row>
     <row r="18" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B18" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>88</v>
       </c>
       <c r="D18" s="7">
-        <v>2550.75</v>
+        <v>2577.54</v>
       </c>
       <c r="F18">
         <v>5</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="19" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B19" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>88</v>
       </c>
       <c r="D19" s="7">
-        <v>3226.53</v>
+        <v>2550.75</v>
       </c>
       <c r="F19">
         <v>5</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="20" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="B20" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>88</v>
       </c>
       <c r="D20" s="7">
-        <v>3611.43</v>
+        <v>3226.53</v>
       </c>
       <c r="F20">
         <v>5</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
     </row>
     <row r="21" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B21" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>88</v>
       </c>
       <c r="D21" s="7">
-        <v>3828.73</v>
+        <v>3611.43</v>
       </c>
       <c r="F21">
         <v>5</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="22" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="B22" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>88</v>
       </c>
       <c r="D22" s="7">
-        <v>4020.83</v>
+        <v>3828.73</v>
       </c>
       <c r="F22">
         <v>5</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
     </row>
     <row r="23" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B23" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>88</v>
       </c>
       <c r="D23" s="7">
-        <v>4020.91</v>
+        <v>4020.83</v>
       </c>
       <c r="F23">
         <v>5</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="24" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="6">
-        <v>10089</v>
+      <c r="A24" t="s">
+        <v>74</v>
       </c>
       <c r="B24" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>88</v>
       </c>
       <c r="D24" s="7">
+        <v>4020.91</v>
+      </c>
+      <c r="F24">
+        <v>5</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A25" s="6">
+        <v>10089</v>
+      </c>
+      <c r="B25" t="s">
+        <v>87</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="D25" s="7">
         <v>4386.92</v>
       </c>
-      <c r="F24">
-        <v>5</v>
-      </c>
-      <c r="G24" s="2" t="s">
+      <c r="F25">
+        <v>5</v>
+      </c>
+      <c r="G25" s="2" t="s">
         <v>98</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="B25" t="s">
-        <v>99</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="D25">
-        <v>728.72</v>
-      </c>
-      <c r="F25">
-        <v>5</v>
-      </c>
-      <c r="G25" s="2" t="s">
-        <v>108</v>
       </c>
     </row>
     <row r="26" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B26" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>103</v>
       </c>
       <c r="D26">
-        <v>474.36</v>
+        <v>728.72</v>
       </c>
       <c r="F26">
         <v>5</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="27" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B27" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>103</v>
       </c>
       <c r="D27">
-        <v>522.48</v>
+        <v>474.36</v>
       </c>
       <c r="F27">
         <v>5</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="28" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B28" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>103</v>
       </c>
       <c r="D28">
+        <v>522.48</v>
+      </c>
+      <c r="F28">
+        <v>5</v>
+      </c>
+      <c r="G28" s="2" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A29" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="B29" t="s">
+        <v>102</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="D29">
         <v>653.98</v>
       </c>
-      <c r="F28">
-        <v>5</v>
-      </c>
-      <c r="G28" s="2" t="s">
+      <c r="F29">
+        <v>5</v>
+      </c>
+      <c r="G29" s="2" t="s">
         <v>111</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="8" t="s">
-        <v>112</v>
-      </c>
-      <c r="B29" s="8" t="s">
-        <v>153</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="D29">
-        <v>172.59</v>
-      </c>
-      <c r="F29">
-        <v>5</v>
-      </c>
-      <c r="G29" s="2" t="s">
-        <v>193</v>
       </c>
     </row>
     <row r="30" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="8" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B30" s="8" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>152</v>
@@ -1671,789 +1662,798 @@
         <v>5</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="31" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="8" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B31" s="8" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C31" s="2" t="s">
         <v>152</v>
       </c>
       <c r="D31">
-        <v>21.69</v>
+        <v>172.59</v>
       </c>
       <c r="F31">
         <v>5</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="32" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="8" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B32" s="8" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C32" s="2" t="s">
         <v>152</v>
       </c>
       <c r="D32">
-        <v>198.99</v>
+        <v>21.69</v>
       </c>
       <c r="F32">
         <v>5</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="33" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="8" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B33" s="8" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C33" s="2" t="s">
         <v>152</v>
       </c>
       <c r="D33">
-        <v>144.99</v>
+        <v>198.99</v>
       </c>
       <c r="F33">
         <v>5</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="34" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="8" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B34" s="8" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C34" s="2" t="s">
         <v>152</v>
       </c>
       <c r="D34">
-        <v>42.99</v>
+        <v>144.99</v>
       </c>
       <c r="F34">
         <v>5</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="35" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="8" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B35" s="8" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C35" s="2" t="s">
         <v>152</v>
       </c>
       <c r="D35">
-        <v>165</v>
+        <v>42.99</v>
       </c>
       <c r="F35">
         <v>5</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="36" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="8" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B36" s="8" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C36" s="2" t="s">
         <v>152</v>
       </c>
       <c r="D36">
-        <v>24</v>
+        <v>165</v>
       </c>
       <c r="F36">
         <v>5</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="37" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="8" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B37" s="8" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C37" s="2" t="s">
         <v>152</v>
       </c>
       <c r="D37">
-        <v>168</v>
+        <v>24</v>
       </c>
       <c r="F37">
         <v>5</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="38" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="8" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B38" s="8" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C38" s="2" t="s">
         <v>152</v>
       </c>
       <c r="D38">
-        <v>150</v>
+        <v>168</v>
       </c>
       <c r="F38">
         <v>5</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="39" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="8" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B39" s="8" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C39" s="2" t="s">
         <v>152</v>
       </c>
       <c r="D39">
-        <v>179.4</v>
+        <v>150</v>
       </c>
       <c r="F39">
         <v>5</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="40" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="8" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B40" s="8" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C40" s="2" t="s">
         <v>152</v>
       </c>
       <c r="D40">
-        <v>300</v>
+        <v>179.4</v>
       </c>
       <c r="F40">
         <v>5</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="41" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="8" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B41" s="8" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C41" s="2" t="s">
         <v>152</v>
       </c>
       <c r="D41">
-        <v>225</v>
+        <v>300</v>
       </c>
       <c r="F41">
         <v>5</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="42" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="8" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B42" s="8" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C42" s="2" t="s">
         <v>152</v>
       </c>
       <c r="D42">
-        <v>129.99599999999998</v>
+        <v>225</v>
       </c>
       <c r="F42">
         <v>5</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="43" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="8" t="s">
-        <v>126</v>
+        <v>240</v>
       </c>
       <c r="B43" s="8" t="s">
-        <v>167</v>
-      </c>
-      <c r="C43" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="D43">
-        <v>300</v>
-      </c>
-      <c r="F43">
-        <v>5</v>
+        <v>234</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>207</v>
+        <v>236</v>
       </c>
     </row>
     <row r="44" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="8" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="B44" s="8" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="C44" s="2" t="s">
         <v>152</v>
       </c>
       <c r="D44">
-        <v>10.38</v>
+        <v>129.99599999999998</v>
       </c>
       <c r="F44">
         <v>5</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
     </row>
     <row r="45" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="8" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="B45" s="8" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="C45" s="2" t="s">
         <v>152</v>
       </c>
       <c r="D45">
-        <v>52.8</v>
+        <v>300</v>
       </c>
       <c r="F45">
         <v>5</v>
       </c>
       <c r="G45" s="2" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
     </row>
     <row r="46" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="8" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="B46" s="8" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="C46" s="2" t="s">
         <v>152</v>
       </c>
       <c r="D46">
-        <v>255</v>
+        <v>10.38</v>
       </c>
       <c r="F46">
         <v>5</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
     </row>
     <row r="47" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="8" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="B47" s="8" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="C47" s="2" t="s">
         <v>152</v>
       </c>
       <c r="D47">
-        <v>39</v>
+        <v>52.8</v>
       </c>
       <c r="F47">
         <v>5</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
     </row>
     <row r="48" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="8" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="B48" s="8" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="C48" s="2" t="s">
         <v>152</v>
       </c>
       <c r="D48">
-        <v>128.4</v>
+        <v>255</v>
       </c>
       <c r="F48">
         <v>5</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
     </row>
     <row r="49" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="8" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="B49" s="8" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="C49" s="2" t="s">
         <v>152</v>
       </c>
       <c r="D49">
-        <v>127.19999999999999</v>
+        <v>39</v>
       </c>
       <c r="F49">
         <v>5</v>
       </c>
       <c r="G49" s="2" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
     </row>
     <row r="50" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="8" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="B50" s="8" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="C50" s="2" t="s">
         <v>152</v>
       </c>
       <c r="D50">
-        <v>225</v>
+        <v>128.4</v>
       </c>
       <c r="F50">
         <v>5</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
     </row>
     <row r="51" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="8" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B51" s="8" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="C51" s="2" t="s">
         <v>152</v>
       </c>
       <c r="D51">
-        <v>180</v>
+        <v>127.19999999999999</v>
       </c>
       <c r="F51">
         <v>5</v>
       </c>
       <c r="G51" s="2" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
     </row>
     <row r="52" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="8" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B52" s="8" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="C52" s="2" t="s">
         <v>152</v>
       </c>
       <c r="D52">
-        <v>26.255999999999997</v>
+        <v>225</v>
       </c>
       <c r="F52">
         <v>5</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
     </row>
     <row r="53" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="8" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="B53" s="8" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="C53" s="2" t="s">
         <v>152</v>
       </c>
       <c r="D53">
-        <v>202.79999999999998</v>
+        <v>180</v>
       </c>
       <c r="F53">
         <v>5</v>
       </c>
       <c r="G53" s="2" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
     </row>
     <row r="54" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="8" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="B54" s="8" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="C54" s="2" t="s">
         <v>152</v>
       </c>
       <c r="D54">
-        <v>13.56</v>
+        <v>26.255999999999997</v>
       </c>
       <c r="F54">
         <v>5</v>
       </c>
       <c r="G54" s="2" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
     </row>
     <row r="55" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="8" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="B55" s="8" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="C55" s="2" t="s">
         <v>152</v>
       </c>
       <c r="D55">
-        <v>127.19999999999999</v>
+        <v>202.79999999999998</v>
       </c>
       <c r="F55">
         <v>5</v>
       </c>
       <c r="G55" s="2" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
     </row>
     <row r="56" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="8" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="B56" s="8" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C56" s="2" t="s">
         <v>152</v>
       </c>
       <c r="D56">
-        <v>150</v>
+        <v>13.56</v>
       </c>
       <c r="F56">
         <v>5</v>
       </c>
       <c r="G56" s="2" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
     </row>
     <row r="57" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="8" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="B57" s="8" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="C57" s="2" t="s">
         <v>152</v>
       </c>
       <c r="D57">
-        <v>156</v>
+        <v>127.19999999999999</v>
       </c>
       <c r="F57">
         <v>5</v>
       </c>
       <c r="G57" s="2" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
     </row>
     <row r="58" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="8" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="B58" s="8" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="C58" s="2" t="s">
         <v>152</v>
       </c>
       <c r="D58">
-        <v>216</v>
+        <v>150</v>
       </c>
       <c r="F58">
         <v>5</v>
       </c>
       <c r="G58" s="2" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
     </row>
     <row r="59" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="8" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="B59" s="8" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C59" s="2" t="s">
         <v>152</v>
       </c>
       <c r="D59">
-        <v>90</v>
+        <v>156</v>
       </c>
       <c r="F59">
         <v>5</v>
       </c>
       <c r="G59" s="2" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
     </row>
     <row r="60" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60" s="8" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="B60" s="8" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="C60" s="2" t="s">
         <v>152</v>
       </c>
       <c r="D60">
-        <v>127.19999999999999</v>
+        <v>216</v>
       </c>
       <c r="F60">
         <v>5</v>
       </c>
       <c r="G60" s="2" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="61" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="8" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="B61" s="8" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="C61" s="2" t="s">
         <v>152</v>
       </c>
       <c r="D61">
-        <v>144</v>
+        <v>90</v>
       </c>
       <c r="F61">
         <v>5</v>
       </c>
       <c r="G61" s="2" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
     </row>
     <row r="62" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="8" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="B62" s="8" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="C62" s="2" t="s">
         <v>152</v>
       </c>
       <c r="D62">
-        <v>75.599999999999994</v>
+        <v>127.19999999999999</v>
       </c>
       <c r="F62">
         <v>5</v>
       </c>
       <c r="G62" s="2" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
     </row>
     <row r="63" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A63" s="8" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="B63" s="8" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C63" s="2" t="s">
         <v>152</v>
       </c>
       <c r="D63">
-        <v>194.4</v>
+        <v>144</v>
       </c>
       <c r="F63">
         <v>5</v>
       </c>
       <c r="G63" s="2" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
     </row>
     <row r="64" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A64" s="8" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="B64" s="8" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="C64" s="2" t="s">
         <v>152</v>
       </c>
       <c r="D64">
-        <v>285</v>
+        <v>75.599999999999994</v>
       </c>
       <c r="F64">
         <v>5</v>
       </c>
       <c r="G64" s="2" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="65" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" s="8" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="B65" s="8" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="C65" s="2" t="s">
         <v>152</v>
       </c>
       <c r="D65">
-        <v>18.72</v>
+        <v>194.4</v>
       </c>
       <c r="F65">
         <v>5</v>
       </c>
       <c r="G65" s="2" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
     </row>
     <row r="66" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A66" s="8" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="B66" s="8" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="C66" s="2" t="s">
         <v>152</v>
       </c>
       <c r="D66">
-        <v>30</v>
+        <v>285</v>
       </c>
       <c r="F66">
         <v>5</v>
       </c>
       <c r="G66" s="2" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
     </row>
     <row r="67" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A67" s="8" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="B67" s="8" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="C67" s="2" t="s">
         <v>152</v>
       </c>
       <c r="D67">
-        <v>24.479999999999997</v>
+        <v>18.72</v>
       </c>
       <c r="F67">
         <v>5</v>
       </c>
       <c r="G67" s="2" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
     </row>
     <row r="68" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A68" s="8" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="B68" s="8" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="C68" s="2" t="s">
         <v>152</v>
       </c>
       <c r="D68">
-        <v>90</v>
+        <v>30</v>
       </c>
       <c r="F68">
         <v>5</v>
       </c>
       <c r="G68" s="2" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
     </row>
     <row r="69" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A69" s="8" t="s">
-        <v>239</v>
+        <v>150</v>
       </c>
       <c r="B69" s="8" t="s">
-        <v>233</v>
+        <v>191</v>
+      </c>
+      <c r="C69" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="D69">
+        <v>24.479999999999997</v>
+      </c>
+      <c r="F69">
+        <v>5</v>
       </c>
       <c r="G69" s="2" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
     </row>
     <row r="70" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A70" s="8" t="s">
-        <v>240</v>
+        <v>151</v>
       </c>
       <c r="B70" s="8" t="s">
-        <v>234</v>
+        <v>192</v>
+      </c>
+      <c r="C70" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="D70">
+        <v>90</v>
+      </c>
+      <c r="F70">
+        <v>5</v>
       </c>
       <c r="G70" s="2" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
     </row>
     <row r="71" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">

--- a/urunler.xlsx
+++ b/urunler.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\Githup\portal\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8CEBC48B-A5B3-4380-B0D2-B22BF65EB277}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D98DD56-BFA3-4186-9051-989DDC4347EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1065,7 +1065,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:G71"/>
+  <dimension ref="A1:G73"/>
   <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="41.140625" customWidth="1"/>
@@ -1294,17 +1294,6 @@
         <v>64</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="8" t="s">
-        <v>239</v>
-      </c>
-      <c r="B12" s="8" t="s">
-        <v>233</v>
-      </c>
-      <c r="G12" s="2" t="s">
-        <v>235</v>
-      </c>
-    </row>
     <row r="13" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>66</v>
@@ -1905,17 +1894,6 @@
         <v>205</v>
       </c>
     </row>
-    <row r="43" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A43" s="8" t="s">
-        <v>240</v>
-      </c>
-      <c r="B43" s="8" t="s">
-        <v>234</v>
-      </c>
-      <c r="G43" s="2" t="s">
-        <v>236</v>
-      </c>
-    </row>
     <row r="44" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="8" t="s">
         <v>125</v>
@@ -2465,6 +2443,28 @@
       </c>
       <c r="G71" s="2" t="s">
         <v>238</v>
+      </c>
+    </row>
+    <row r="72" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A72" s="8" t="s">
+        <v>239</v>
+      </c>
+      <c r="B72" s="8" t="s">
+        <v>233</v>
+      </c>
+      <c r="G72" s="2" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="73" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A73" s="8" t="s">
+        <v>240</v>
+      </c>
+      <c r="B73" s="8" t="s">
+        <v>234</v>
+      </c>
+      <c r="G73" s="2" t="s">
+        <v>236</v>
       </c>
     </row>
   </sheetData>

--- a/urunler.xlsx
+++ b/urunler.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\Githup\portal\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D98DD56-BFA3-4186-9051-989DDC4347EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A22F93D-30BF-4483-9077-C28E52F98476}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="311" uniqueCount="242">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="301" uniqueCount="232">
   <si>
     <t>urun_no</t>
   </si>
@@ -172,36 +172,6 @@
   </si>
   <si>
     <t>BANNER</t>
-  </si>
-  <si>
-    <t>152,00 EURO</t>
-  </si>
-  <si>
-    <t>175,00 EURO</t>
-  </si>
-  <si>
-    <t>191,00 EURO</t>
-  </si>
-  <si>
-    <t>216,00 EURO</t>
-  </si>
-  <si>
-    <t>256,00 EURO</t>
-  </si>
-  <si>
-    <t>81,00 EURO</t>
-  </si>
-  <si>
-    <t>136,00 EURO</t>
-  </si>
-  <si>
-    <t>98,00 EURO</t>
-  </si>
-  <si>
-    <t>116,00 EURO</t>
-  </si>
-  <si>
-    <t>122,00 EURO</t>
   </si>
   <si>
     <t>56001.PNG</t>
@@ -766,9 +736,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="44" formatCode="_-&quot;₺&quot;* #,##0.00_-;\-&quot;₺&quot;* #,##0.00_-;_-&quot;₺&quot;* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="164" formatCode="#,##0.00;[Red]#,##0.00"/>
+    <numFmt numFmtId="165" formatCode="_-[$€-2]\ * #,##0.00_-;\-[$€-2]\ * #,##0.00_-;_-[$€-2]\ * &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="166" formatCode="_-[$₺-41F]* #,##0.00_-;\-[$₺-41F]* #,##0.00_-;_-[$₺-41F]* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
   <fonts count="6" x14ac:knownFonts="1">
     <font>
@@ -832,20 +803,30 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="44" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1065,7 +1046,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:G73"/>
+  <dimension ref="A1:G71"/>
   <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="41.140625" customWidth="1"/>
@@ -1096,456 +1077,485 @@
       </c>
     </row>
     <row r="2" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A2" s="5">
+      <c r="A2" s="7">
         <v>56001</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="4" t="s">
         <v>35</v>
       </c>
       <c r="C2" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="D2" s="9">
+        <v>152</v>
+      </c>
+      <c r="E2" s="3"/>
+      <c r="F2" s="4">
+        <v>5</v>
+      </c>
+      <c r="G2" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="E2" s="3"/>
-      <c r="F2" s="1">
-        <v>5</v>
-      </c>
-      <c r="G2" s="4" t="s">
-        <v>56</v>
-      </c>
     </row>
     <row r="3" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A3" s="5">
+      <c r="A3" s="7">
         <v>57001</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B3" s="4" t="s">
         <v>36</v>
       </c>
       <c r="C3" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="D3" s="3" t="s">
-        <v>47</v>
+      <c r="D3" s="9">
+        <v>175</v>
       </c>
       <c r="E3" s="3"/>
-      <c r="F3" s="1">
+      <c r="F3" s="4">
         <v>5</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="6">
+      <c r="A4" s="8">
         <v>58001</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="2" t="s">
         <v>37</v>
       </c>
       <c r="C4" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="D4" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="F4">
+      <c r="D4" s="10">
+        <v>191</v>
+      </c>
+      <c r="E4" s="2"/>
+      <c r="F4" s="2">
         <v>5</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="6">
+      <c r="A5" s="8">
         <v>59502</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="2" t="s">
         <v>38</v>
       </c>
       <c r="C5" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="D5" s="2" t="s">
-        <v>49</v>
-      </c>
+      <c r="D5" s="10">
+        <v>216</v>
+      </c>
+      <c r="E5" s="2"/>
+      <c r="F5" s="2"/>
       <c r="G5" s="2" t="s">
-        <v>58</v>
+        <v>48</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="6">
+      <c r="A6" s="8">
         <v>60501</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" s="2" t="s">
         <v>39</v>
       </c>
       <c r="C6" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="D6" s="2" t="s">
-        <v>50</v>
-      </c>
+      <c r="D6" s="10">
+        <v>256</v>
+      </c>
+      <c r="E6" s="2"/>
       <c r="F6" s="4">
         <v>5</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>59</v>
+        <v>49</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="6">
+      <c r="A7" s="8">
         <v>56009</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="2" t="s">
         <v>40</v>
       </c>
       <c r="C7" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="D7" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="F7">
+      <c r="D7" s="10">
+        <v>81</v>
+      </c>
+      <c r="E7" s="2"/>
+      <c r="F7" s="2">
         <v>5</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>60</v>
+        <v>50</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="6">
+      <c r="A8" s="8">
         <v>57011</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B8" s="2" t="s">
         <v>41</v>
       </c>
       <c r="C8" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="D8" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="F8">
+      <c r="D8" s="10">
+        <v>136</v>
+      </c>
+      <c r="E8" s="2"/>
+      <c r="F8" s="2">
         <v>5</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>61</v>
+        <v>51</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="6">
+      <c r="A9" s="8">
         <v>57044</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B9" s="2" t="s">
         <v>42</v>
       </c>
       <c r="C9" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="D9" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="F9">
+      <c r="D9" s="10">
+        <v>98</v>
+      </c>
+      <c r="E9" s="2"/>
+      <c r="F9" s="2">
         <v>5</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>62</v>
+        <v>52</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="6">
+      <c r="A10" s="8">
         <v>58014</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B10" s="2" t="s">
         <v>43</v>
       </c>
       <c r="C10" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="D10" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="F10">
+      <c r="D10" s="10">
+        <v>116</v>
+      </c>
+      <c r="E10" s="2"/>
+      <c r="F10" s="2">
         <v>5</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="6">
+      <c r="A11" s="8">
         <v>59533</v>
       </c>
-      <c r="B11" t="s">
+      <c r="B11" s="2" t="s">
         <v>44</v>
       </c>
       <c r="C11" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="D11" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="F11">
+      <c r="D11" s="10">
+        <v>122</v>
+      </c>
+      <c r="E11" s="2"/>
+      <c r="F11" s="2">
         <v>5</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>64</v>
+        <v>54</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>56</v>
+      </c>
+      <c r="B12" t="s">
+        <v>65</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="D12" s="11">
+        <v>6480.92</v>
+      </c>
+      <c r="F12">
+        <v>5</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
+        <v>57</v>
+      </c>
+      <c r="B13" t="s">
         <v>66</v>
       </c>
-      <c r="B13" t="s">
-        <v>75</v>
-      </c>
       <c r="C13" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="D13" s="7">
-        <v>6480.92</v>
+        <v>78</v>
+      </c>
+      <c r="D13" s="11">
+        <v>8841.6200000000008</v>
       </c>
       <c r="F13">
         <v>5</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
+        <v>58</v>
+      </c>
+      <c r="B14" t="s">
         <v>67</v>
       </c>
-      <c r="B14" t="s">
-        <v>76</v>
-      </c>
       <c r="C14" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="D14" s="7">
-        <v>8841.6200000000008</v>
+        <v>78</v>
+      </c>
+      <c r="D14" s="11">
+        <v>8520.89</v>
       </c>
       <c r="F14">
         <v>5</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>90</v>
+        <v>81</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
+        <v>59</v>
+      </c>
+      <c r="B15" t="s">
         <v>68</v>
       </c>
-      <c r="B15" t="s">
-        <v>77</v>
-      </c>
       <c r="C15" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="D15" s="7">
-        <v>8520.89</v>
+        <v>78</v>
+      </c>
+      <c r="D15" s="11">
+        <v>9540.83</v>
       </c>
       <c r="F15">
         <v>5</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>91</v>
+        <v>82</v>
       </c>
     </row>
     <row r="16" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
+        <v>57</v>
+      </c>
+      <c r="B16" t="s">
         <v>69</v>
       </c>
-      <c r="B16" t="s">
+      <c r="C16" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="C16" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="D16" s="7">
-        <v>9540.83</v>
+      <c r="D16" s="11">
+        <v>7620.91</v>
       </c>
       <c r="F16">
         <v>5</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>92</v>
+        <v>80</v>
       </c>
     </row>
     <row r="17" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="B17" t="s">
-        <v>79</v>
+        <v>70</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="D17" s="7">
-        <v>7620.91</v>
+        <v>78</v>
+      </c>
+      <c r="D17" s="11">
+        <v>2577.54</v>
       </c>
       <c r="F17">
         <v>5</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
     </row>
     <row r="18" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="B18" t="s">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="D18" s="7">
-        <v>2577.54</v>
+        <v>78</v>
+      </c>
+      <c r="D18" s="11">
+        <v>2550.75</v>
       </c>
       <c r="F18">
         <v>5</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>93</v>
+        <v>84</v>
       </c>
     </row>
     <row r="19" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="B19" t="s">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="D19" s="7">
-        <v>2550.75</v>
+        <v>78</v>
+      </c>
+      <c r="D19" s="11">
+        <v>3226.53</v>
       </c>
       <c r="F19">
         <v>5</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>94</v>
+        <v>85</v>
       </c>
     </row>
     <row r="20" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>72</v>
+        <v>56</v>
       </c>
       <c r="B20" t="s">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="D20" s="7">
-        <v>3226.53</v>
+        <v>78</v>
+      </c>
+      <c r="D20" s="11">
+        <v>3611.43</v>
       </c>
       <c r="F20">
         <v>5</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>95</v>
+        <v>79</v>
       </c>
     </row>
     <row r="21" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>66</v>
+        <v>57</v>
       </c>
       <c r="B21" t="s">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="D21" s="7">
-        <v>3611.43</v>
+        <v>78</v>
+      </c>
+      <c r="D21" s="11">
+        <v>3828.73</v>
       </c>
       <c r="F21">
         <v>5</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
     </row>
     <row r="22" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="B22" t="s">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="D22" s="7">
-        <v>3828.73</v>
+        <v>78</v>
+      </c>
+      <c r="D22" s="11">
+        <v>4020.83</v>
       </c>
       <c r="F22">
         <v>5</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
     </row>
     <row r="23" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="B23" t="s">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="C23" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="D23" s="11">
+        <v>4020.91</v>
+      </c>
+      <c r="F23">
+        <v>5</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A24" s="5">
+        <v>10089</v>
+      </c>
+      <c r="B24" t="s">
+        <v>77</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="D24" s="11">
+        <v>4386.92</v>
+      </c>
+      <c r="F24">
+        <v>5</v>
+      </c>
+      <c r="G24" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="D23" s="7">
-        <v>4020.83</v>
-      </c>
-      <c r="F23">
-        <v>5</v>
-      </c>
-      <c r="G23" s="2" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" t="s">
-        <v>74</v>
-      </c>
-      <c r="B24" t="s">
-        <v>86</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="D24" s="7">
-        <v>4020.91</v>
-      </c>
-      <c r="F24">
-        <v>5</v>
-      </c>
-      <c r="G24" s="2" t="s">
-        <v>97</v>
-      </c>
     </row>
     <row r="25" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="6">
-        <v>10089</v>
+      <c r="A25" s="2" t="s">
+        <v>94</v>
       </c>
       <c r="B25" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="D25" s="7">
-        <v>4386.92</v>
+        <v>93</v>
+      </c>
+      <c r="D25" s="12">
+        <v>728.72</v>
       </c>
       <c r="F25">
         <v>5</v>
@@ -1556,915 +1566,895 @@
     </row>
     <row r="26" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="2" t="s">
-        <v>104</v>
+        <v>95</v>
       </c>
       <c r="B26" t="s">
+        <v>90</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="D26" s="12">
+        <v>474.36</v>
+      </c>
+      <c r="F26">
+        <v>5</v>
+      </c>
+      <c r="G26" s="2" t="s">
         <v>99</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="D26">
-        <v>728.72</v>
-      </c>
-      <c r="F26">
-        <v>5</v>
-      </c>
-      <c r="G26" s="2" t="s">
-        <v>108</v>
       </c>
     </row>
     <row r="27" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="2" t="s">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="B27" t="s">
+        <v>91</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="D27" s="12">
+        <v>522.48</v>
+      </c>
+      <c r="F27">
+        <v>5</v>
+      </c>
+      <c r="G27" s="2" t="s">
         <v>100</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="D27">
-        <v>474.36</v>
-      </c>
-      <c r="F27">
-        <v>5</v>
-      </c>
-      <c r="G27" s="2" t="s">
-        <v>109</v>
       </c>
     </row>
     <row r="28" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="B28" t="s">
+        <v>92</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="D28" s="12">
+        <v>653.98</v>
+      </c>
+      <c r="F28">
+        <v>5</v>
+      </c>
+      <c r="G28" s="2" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A29" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="B29" s="6" t="s">
+        <v>143</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="D29" s="12">
+        <v>172.59</v>
+      </c>
+      <c r="F29">
+        <v>5</v>
+      </c>
+      <c r="G29" s="2" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A30" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="B30" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="D30" s="12">
+        <v>172.59</v>
+      </c>
+      <c r="F30">
+        <v>5</v>
+      </c>
+      <c r="G30" s="2" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A31" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="B31" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="D31" s="12">
+        <v>21.69</v>
+      </c>
+      <c r="F31">
+        <v>5</v>
+      </c>
+      <c r="G31" s="2" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A32" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="B32" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="D32" s="12">
+        <v>198.99</v>
+      </c>
+      <c r="F32">
+        <v>5</v>
+      </c>
+      <c r="G32" s="2" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A33" s="6" t="s">
         <v>106</v>
       </c>
-      <c r="B28" t="s">
-        <v>101</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="D28">
-        <v>522.48</v>
-      </c>
-      <c r="F28">
-        <v>5</v>
-      </c>
-      <c r="G28" s="2" t="s">
+      <c r="B33" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="D33" s="12">
+        <v>144.99</v>
+      </c>
+      <c r="F33">
+        <v>5</v>
+      </c>
+      <c r="G33" s="2" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A34" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="B34" s="6" t="s">
+        <v>148</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="D34" s="12">
+        <v>42.99</v>
+      </c>
+      <c r="F34">
+        <v>5</v>
+      </c>
+      <c r="G34" s="2" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A35" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="B35" s="6" t="s">
+        <v>149</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="D35" s="12">
+        <v>165</v>
+      </c>
+      <c r="F35">
+        <v>5</v>
+      </c>
+      <c r="G35" s="2" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A36" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="B36" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="D36" s="12">
+        <v>24</v>
+      </c>
+      <c r="F36">
+        <v>5</v>
+      </c>
+      <c r="G36" s="2" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A37" s="6" t="s">
         <v>110</v>
       </c>
-    </row>
-    <row r="29" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="B29" t="s">
-        <v>102</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="D29">
-        <v>653.98</v>
-      </c>
-      <c r="F29">
-        <v>5</v>
-      </c>
-      <c r="G29" s="2" t="s">
+      <c r="B37" s="6" t="s">
+        <v>151</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="D37" s="12">
+        <v>168</v>
+      </c>
+      <c r="F37">
+        <v>5</v>
+      </c>
+      <c r="G37" s="2" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A38" s="6" t="s">
         <v>111</v>
       </c>
-    </row>
-    <row r="30" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="8" t="s">
+      <c r="B38" s="6" t="s">
+        <v>152</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="D38" s="12">
+        <v>150</v>
+      </c>
+      <c r="F38">
+        <v>5</v>
+      </c>
+      <c r="G38" s="2" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A39" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="B30" s="8" t="s">
+      <c r="B39" s="6" t="s">
         <v>153</v>
       </c>
-      <c r="C30" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="D30">
-        <v>172.59</v>
-      </c>
-      <c r="F30">
-        <v>5</v>
-      </c>
-      <c r="G30" s="2" t="s">
+      <c r="C39" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="D39" s="12">
+        <v>179.4</v>
+      </c>
+      <c r="F39">
+        <v>5</v>
+      </c>
+      <c r="G39" s="2" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="31" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="8" t="s">
+    <row r="40" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A40" s="6" t="s">
         <v>113</v>
       </c>
-      <c r="B31" s="8" t="s">
+      <c r="B40" s="6" t="s">
         <v>154</v>
       </c>
-      <c r="C31" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="D31">
-        <v>172.59</v>
-      </c>
-      <c r="F31">
-        <v>5</v>
-      </c>
-      <c r="G31" s="2" t="s">
+      <c r="C40" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="D40" s="12">
+        <v>300</v>
+      </c>
+      <c r="F40">
+        <v>5</v>
+      </c>
+      <c r="G40" s="2" t="s">
         <v>194</v>
       </c>
     </row>
-    <row r="32" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="8" t="s">
+    <row r="41" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A41" s="6" t="s">
         <v>114</v>
       </c>
-      <c r="B32" s="8" t="s">
+      <c r="B41" s="6" t="s">
         <v>155</v>
       </c>
-      <c r="C32" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="D32">
-        <v>21.69</v>
-      </c>
-      <c r="F32">
-        <v>5</v>
-      </c>
-      <c r="G32" s="2" t="s">
+      <c r="C41" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="D41" s="12">
+        <v>225</v>
+      </c>
+      <c r="F41">
+        <v>5</v>
+      </c>
+      <c r="G41" s="2" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="33" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="8" t="s">
+    <row r="42" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A42" s="6" t="s">
         <v>115</v>
       </c>
-      <c r="B33" s="8" t="s">
+      <c r="B42" s="6" t="s">
         <v>156</v>
       </c>
-      <c r="C33" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="D33">
-        <v>198.99</v>
-      </c>
-      <c r="F33">
-        <v>5</v>
-      </c>
-      <c r="G33" s="2" t="s">
+      <c r="C42" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="D42" s="12">
+        <v>129.99599999999998</v>
+      </c>
+      <c r="F42">
+        <v>5</v>
+      </c>
+      <c r="G42" s="2" t="s">
         <v>196</v>
       </c>
     </row>
-    <row r="34" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="8" t="s">
+    <row r="43" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A43" s="6" t="s">
         <v>116</v>
       </c>
-      <c r="B34" s="8" t="s">
+      <c r="B43" s="6" t="s">
         <v>157</v>
       </c>
-      <c r="C34" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="D34">
-        <v>144.99</v>
-      </c>
-      <c r="F34">
-        <v>5</v>
-      </c>
-      <c r="G34" s="2" t="s">
+      <c r="C43" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="D43" s="12">
+        <v>300</v>
+      </c>
+      <c r="F43">
+        <v>5</v>
+      </c>
+      <c r="G43" s="2" t="s">
         <v>197</v>
       </c>
     </row>
-    <row r="35" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="8" t="s">
+    <row r="44" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A44" s="6" t="s">
         <v>117</v>
       </c>
-      <c r="B35" s="8" t="s">
+      <c r="B44" s="6" t="s">
         <v>158</v>
       </c>
-      <c r="C35" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="D35">
-        <v>42.99</v>
-      </c>
-      <c r="F35">
-        <v>5</v>
-      </c>
-      <c r="G35" s="2" t="s">
+      <c r="C44" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="D44" s="12">
+        <v>10.38</v>
+      </c>
+      <c r="F44">
+        <v>5</v>
+      </c>
+      <c r="G44" s="2" t="s">
         <v>198</v>
       </c>
     </row>
-    <row r="36" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="8" t="s">
+    <row r="45" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A45" s="6" t="s">
         <v>118</v>
       </c>
-      <c r="B36" s="8" t="s">
+      <c r="B45" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="C36" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="D36">
+      <c r="C45" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="D45" s="12">
+        <v>52.8</v>
+      </c>
+      <c r="F45">
+        <v>5</v>
+      </c>
+      <c r="G45" s="2" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A46" s="6" t="s">
+        <v>119</v>
+      </c>
+      <c r="B46" s="6" t="s">
+        <v>160</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="D46" s="12">
+        <v>255</v>
+      </c>
+      <c r="F46">
+        <v>5</v>
+      </c>
+      <c r="G46" s="2" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A47" s="6" t="s">
+        <v>120</v>
+      </c>
+      <c r="B47" s="6" t="s">
+        <v>161</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="D47" s="12">
+        <v>39</v>
+      </c>
+      <c r="F47">
+        <v>5</v>
+      </c>
+      <c r="G47" s="2" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A48" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="B48" s="6" t="s">
+        <v>162</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="D48" s="12">
+        <v>128.4</v>
+      </c>
+      <c r="F48">
+        <v>5</v>
+      </c>
+      <c r="G48" s="2" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A49" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="B49" s="6" t="s">
+        <v>163</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="D49" s="12">
+        <v>127.19999999999999</v>
+      </c>
+      <c r="F49">
+        <v>5</v>
+      </c>
+      <c r="G49" s="2" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A50" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="B50" s="6" t="s">
+        <v>164</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="D50" s="12">
+        <v>225</v>
+      </c>
+      <c r="F50">
+        <v>5</v>
+      </c>
+      <c r="G50" s="2" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A51" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="B51" s="6" t="s">
         <v>165</v>
       </c>
-      <c r="F36">
-        <v>5</v>
-      </c>
-      <c r="G36" s="2" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="8" t="s">
-        <v>119</v>
-      </c>
-      <c r="B37" s="8" t="s">
-        <v>160</v>
-      </c>
-      <c r="C37" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="D37">
-        <v>24</v>
-      </c>
-      <c r="F37">
-        <v>5</v>
-      </c>
-      <c r="G37" s="2" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="8" t="s">
-        <v>120</v>
-      </c>
-      <c r="B38" s="8" t="s">
-        <v>161</v>
-      </c>
-      <c r="C38" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="D38">
+      <c r="C51" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="D51" s="12">
+        <v>180</v>
+      </c>
+      <c r="F51">
+        <v>5</v>
+      </c>
+      <c r="G51" s="2" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A52" s="6" t="s">
+        <v>125</v>
+      </c>
+      <c r="B52" s="6" t="s">
+        <v>166</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="D52" s="12">
+        <v>26.255999999999997</v>
+      </c>
+      <c r="F52">
+        <v>5</v>
+      </c>
+      <c r="G52" s="2" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A53" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="B53" s="6" t="s">
+        <v>167</v>
+      </c>
+      <c r="C53" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="D53" s="12">
+        <v>202.79999999999998</v>
+      </c>
+      <c r="F53">
+        <v>5</v>
+      </c>
+      <c r="G53" s="2" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A54" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="B54" s="6" t="s">
         <v>168</v>
       </c>
-      <c r="F38">
-        <v>5</v>
-      </c>
-      <c r="G38" s="2" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="8" t="s">
-        <v>121</v>
-      </c>
-      <c r="B39" s="8" t="s">
-        <v>162</v>
-      </c>
-      <c r="C39" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="D39">
+      <c r="C54" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="D54" s="12">
+        <v>13.56</v>
+      </c>
+      <c r="F54">
+        <v>5</v>
+      </c>
+      <c r="G54" s="2" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A55" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="B55" s="6" t="s">
+        <v>169</v>
+      </c>
+      <c r="C55" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="D55" s="12">
+        <v>127.19999999999999</v>
+      </c>
+      <c r="F55">
+        <v>5</v>
+      </c>
+      <c r="G55" s="2" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A56" s="6" t="s">
+        <v>129</v>
+      </c>
+      <c r="B56" s="6" t="s">
+        <v>170</v>
+      </c>
+      <c r="C56" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="D56" s="12">
         <v>150</v>
       </c>
-      <c r="F39">
-        <v>5</v>
-      </c>
-      <c r="G39" s="2" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="8" t="s">
-        <v>122</v>
-      </c>
-      <c r="B40" s="8" t="s">
-        <v>163</v>
-      </c>
-      <c r="C40" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="D40">
-        <v>179.4</v>
-      </c>
-      <c r="F40">
-        <v>5</v>
-      </c>
-      <c r="G40" s="2" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="8" t="s">
-        <v>123</v>
-      </c>
-      <c r="B41" s="8" t="s">
-        <v>164</v>
-      </c>
-      <c r="C41" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="D41">
-        <v>300</v>
-      </c>
-      <c r="F41">
-        <v>5</v>
-      </c>
-      <c r="G41" s="2" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="8" t="s">
-        <v>124</v>
-      </c>
-      <c r="B42" s="8" t="s">
-        <v>165</v>
-      </c>
-      <c r="C42" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="D42">
+      <c r="F56">
+        <v>5</v>
+      </c>
+      <c r="G56" s="2" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A57" s="6" t="s">
+        <v>130</v>
+      </c>
+      <c r="B57" s="6" t="s">
+        <v>171</v>
+      </c>
+      <c r="C57" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="D57" s="12">
+        <v>156</v>
+      </c>
+      <c r="F57">
+        <v>5</v>
+      </c>
+      <c r="G57" s="2" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A58" s="6" t="s">
+        <v>131</v>
+      </c>
+      <c r="B58" s="6" t="s">
+        <v>172</v>
+      </c>
+      <c r="C58" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="D58" s="12">
+        <v>216</v>
+      </c>
+      <c r="F58">
+        <v>5</v>
+      </c>
+      <c r="G58" s="2" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A59" s="6" t="s">
+        <v>132</v>
+      </c>
+      <c r="B59" s="6" t="s">
+        <v>173</v>
+      </c>
+      <c r="C59" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="D59" s="12">
+        <v>90</v>
+      </c>
+      <c r="F59">
+        <v>5</v>
+      </c>
+      <c r="G59" s="2" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A60" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="B60" s="6" t="s">
+        <v>174</v>
+      </c>
+      <c r="C60" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="D60" s="12">
+        <v>127.19999999999999</v>
+      </c>
+      <c r="F60">
+        <v>5</v>
+      </c>
+      <c r="G60" s="2" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A61" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="B61" s="6" t="s">
+        <v>175</v>
+      </c>
+      <c r="C61" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="D61" s="12">
+        <v>144</v>
+      </c>
+      <c r="F61">
+        <v>5</v>
+      </c>
+      <c r="G61" s="2" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A62" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="B62" s="6" t="s">
+        <v>176</v>
+      </c>
+      <c r="C62" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="D62" s="12">
+        <v>75.599999999999994</v>
+      </c>
+      <c r="F62">
+        <v>5</v>
+      </c>
+      <c r="G62" s="2" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A63" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="B63" s="6" t="s">
+        <v>177</v>
+      </c>
+      <c r="C63" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="D63" s="12">
+        <v>194.4</v>
+      </c>
+      <c r="F63">
+        <v>5</v>
+      </c>
+      <c r="G63" s="2" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A64" s="6" t="s">
+        <v>137</v>
+      </c>
+      <c r="B64" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="C64" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="D64" s="12">
+        <v>285</v>
+      </c>
+      <c r="F64">
+        <v>5</v>
+      </c>
+      <c r="G64" s="2" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A65" s="6" t="s">
+        <v>138</v>
+      </c>
+      <c r="B65" s="6" t="s">
+        <v>179</v>
+      </c>
+      <c r="C65" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="D65" s="12">
+        <v>18.72</v>
+      </c>
+      <c r="F65">
+        <v>5</v>
+      </c>
+      <c r="G65" s="2" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A66" s="6" t="s">
+        <v>139</v>
+      </c>
+      <c r="B66" s="6" t="s">
+        <v>180</v>
+      </c>
+      <c r="C66" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="D66" s="12">
+        <v>30</v>
+      </c>
+      <c r="F66">
+        <v>5</v>
+      </c>
+      <c r="G66" s="2" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A67" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="B67" s="6" t="s">
+        <v>181</v>
+      </c>
+      <c r="C67" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="D67" s="12">
+        <v>24.479999999999997</v>
+      </c>
+      <c r="F67">
+        <v>5</v>
+      </c>
+      <c r="G67" s="2" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A68" s="6" t="s">
+        <v>141</v>
+      </c>
+      <c r="B68" s="6" t="s">
+        <v>182</v>
+      </c>
+      <c r="C68" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="D68" s="12">
+        <v>90</v>
+      </c>
+      <c r="F68">
+        <v>5</v>
+      </c>
+      <c r="G68" s="2" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="69" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A69" s="6" t="s">
+        <v>231</v>
+      </c>
+      <c r="B69" s="6" t="s">
+        <v>227</v>
+      </c>
+      <c r="G69" s="2" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="70" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A70" s="6" t="s">
+        <v>229</v>
+      </c>
+      <c r="B70" s="6" t="s">
+        <v>223</v>
+      </c>
+      <c r="G70" s="2" t="s">
         <v>225</v>
       </c>
-      <c r="F42">
-        <v>5</v>
-      </c>
-      <c r="G42" s="2" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A44" s="8" t="s">
-        <v>125</v>
-      </c>
-      <c r="B44" s="8" t="s">
-        <v>166</v>
-      </c>
-      <c r="C44" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="D44">
-        <v>129.99599999999998</v>
-      </c>
-      <c r="F44">
-        <v>5</v>
-      </c>
-      <c r="G44" s="2" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A45" s="8" t="s">
-        <v>126</v>
-      </c>
-      <c r="B45" s="8" t="s">
-        <v>167</v>
-      </c>
-      <c r="C45" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="D45">
-        <v>300</v>
-      </c>
-      <c r="F45">
-        <v>5</v>
-      </c>
-      <c r="G45" s="2" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="46" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A46" s="8" t="s">
-        <v>127</v>
-      </c>
-      <c r="B46" s="8" t="s">
-        <v>168</v>
-      </c>
-      <c r="C46" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="D46">
-        <v>10.38</v>
-      </c>
-      <c r="F46">
-        <v>5</v>
-      </c>
-      <c r="G46" s="2" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="47" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A47" s="8" t="s">
-        <v>128</v>
-      </c>
-      <c r="B47" s="8" t="s">
-        <v>169</v>
-      </c>
-      <c r="C47" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="D47">
-        <v>52.8</v>
-      </c>
-      <c r="F47">
-        <v>5</v>
-      </c>
-      <c r="G47" s="2" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="48" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A48" s="8" t="s">
-        <v>129</v>
-      </c>
-      <c r="B48" s="8" t="s">
-        <v>170</v>
-      </c>
-      <c r="C48" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="D48">
-        <v>255</v>
-      </c>
-      <c r="F48">
-        <v>5</v>
-      </c>
-      <c r="G48" s="2" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="49" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A49" s="8" t="s">
-        <v>130</v>
-      </c>
-      <c r="B49" s="8" t="s">
-        <v>171</v>
-      </c>
-      <c r="C49" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="D49">
-        <v>39</v>
-      </c>
-      <c r="F49">
-        <v>5</v>
-      </c>
-      <c r="G49" s="2" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="50" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A50" s="8" t="s">
-        <v>131</v>
-      </c>
-      <c r="B50" s="8" t="s">
-        <v>172</v>
-      </c>
-      <c r="C50" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="D50">
-        <v>128.4</v>
-      </c>
-      <c r="F50">
-        <v>5</v>
-      </c>
-      <c r="G50" s="2" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="51" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A51" s="8" t="s">
-        <v>132</v>
-      </c>
-      <c r="B51" s="8" t="s">
-        <v>173</v>
-      </c>
-      <c r="C51" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="D51">
-        <v>127.19999999999999</v>
-      </c>
-      <c r="F51">
-        <v>5</v>
-      </c>
-      <c r="G51" s="2" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="52" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A52" s="8" t="s">
-        <v>133</v>
-      </c>
-      <c r="B52" s="8" t="s">
-        <v>174</v>
-      </c>
-      <c r="C52" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="D52">
-        <v>225</v>
-      </c>
-      <c r="F52">
-        <v>5</v>
-      </c>
-      <c r="G52" s="2" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="53" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A53" s="8" t="s">
-        <v>134</v>
-      </c>
-      <c r="B53" s="8" t="s">
-        <v>175</v>
-      </c>
-      <c r="C53" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="D53">
-        <v>180</v>
-      </c>
-      <c r="F53">
-        <v>5</v>
-      </c>
-      <c r="G53" s="2" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="54" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A54" s="8" t="s">
-        <v>135</v>
-      </c>
-      <c r="B54" s="8" t="s">
-        <v>176</v>
-      </c>
-      <c r="C54" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="D54">
-        <v>26.255999999999997</v>
-      </c>
-      <c r="F54">
-        <v>5</v>
-      </c>
-      <c r="G54" s="2" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="55" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A55" s="8" t="s">
-        <v>136</v>
-      </c>
-      <c r="B55" s="8" t="s">
-        <v>177</v>
-      </c>
-      <c r="C55" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="D55">
-        <v>202.79999999999998</v>
-      </c>
-      <c r="F55">
-        <v>5</v>
-      </c>
-      <c r="G55" s="2" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="56" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A56" s="8" t="s">
-        <v>137</v>
-      </c>
-      <c r="B56" s="8" t="s">
-        <v>178</v>
-      </c>
-      <c r="C56" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="D56">
-        <v>13.56</v>
-      </c>
-      <c r="F56">
-        <v>5</v>
-      </c>
-      <c r="G56" s="2" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="57" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A57" s="8" t="s">
-        <v>138</v>
-      </c>
-      <c r="B57" s="8" t="s">
-        <v>179</v>
-      </c>
-      <c r="C57" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="D57">
-        <v>127.19999999999999</v>
-      </c>
-      <c r="F57">
-        <v>5</v>
-      </c>
-      <c r="G57" s="2" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="58" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A58" s="8" t="s">
-        <v>139</v>
-      </c>
-      <c r="B58" s="8" t="s">
-        <v>180</v>
-      </c>
-      <c r="C58" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="D58">
-        <v>150</v>
-      </c>
-      <c r="F58">
-        <v>5</v>
-      </c>
-      <c r="G58" s="2" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="59" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A59" s="8" t="s">
-        <v>140</v>
-      </c>
-      <c r="B59" s="8" t="s">
-        <v>181</v>
-      </c>
-      <c r="C59" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="D59">
-        <v>156</v>
-      </c>
-      <c r="F59">
-        <v>5</v>
-      </c>
-      <c r="G59" s="2" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="60" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A60" s="8" t="s">
-        <v>141</v>
-      </c>
-      <c r="B60" s="8" t="s">
-        <v>182</v>
-      </c>
-      <c r="C60" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="D60">
-        <v>216</v>
-      </c>
-      <c r="F60">
-        <v>5</v>
-      </c>
-      <c r="G60" s="2" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="61" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A61" s="8" t="s">
-        <v>142</v>
-      </c>
-      <c r="B61" s="8" t="s">
-        <v>183</v>
-      </c>
-      <c r="C61" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="D61">
-        <v>90</v>
-      </c>
-      <c r="F61">
-        <v>5</v>
-      </c>
-      <c r="G61" s="2" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="62" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A62" s="8" t="s">
-        <v>143</v>
-      </c>
-      <c r="B62" s="8" t="s">
-        <v>184</v>
-      </c>
-      <c r="C62" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="D62">
-        <v>127.19999999999999</v>
-      </c>
-      <c r="F62">
-        <v>5</v>
-      </c>
-      <c r="G62" s="2" t="s">
+    </row>
+    <row r="71" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A71" s="6" t="s">
+        <v>230</v>
+      </c>
+      <c r="B71" s="6" t="s">
         <v>224</v>
       </c>
-    </row>
-    <row r="63" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A63" s="8" t="s">
-        <v>144</v>
-      </c>
-      <c r="B63" s="8" t="s">
-        <v>185</v>
-      </c>
-      <c r="C63" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="D63">
-        <v>144</v>
-      </c>
-      <c r="F63">
-        <v>5</v>
-      </c>
-      <c r="G63" s="2" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="64" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A64" s="8" t="s">
-        <v>145</v>
-      </c>
-      <c r="B64" s="8" t="s">
-        <v>186</v>
-      </c>
-      <c r="C64" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="D64">
-        <v>75.599999999999994</v>
-      </c>
-      <c r="F64">
-        <v>5</v>
-      </c>
-      <c r="G64" s="2" t="s">
+      <c r="G71" s="2" t="s">
         <v>226</v>
-      </c>
-    </row>
-    <row r="65" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A65" s="8" t="s">
-        <v>146</v>
-      </c>
-      <c r="B65" s="8" t="s">
-        <v>187</v>
-      </c>
-      <c r="C65" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="D65">
-        <v>194.4</v>
-      </c>
-      <c r="F65">
-        <v>5</v>
-      </c>
-      <c r="G65" s="2" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="66" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A66" s="8" t="s">
-        <v>147</v>
-      </c>
-      <c r="B66" s="8" t="s">
-        <v>188</v>
-      </c>
-      <c r="C66" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="D66">
-        <v>285</v>
-      </c>
-      <c r="F66">
-        <v>5</v>
-      </c>
-      <c r="G66" s="2" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="67" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A67" s="8" t="s">
-        <v>148</v>
-      </c>
-      <c r="B67" s="8" t="s">
-        <v>189</v>
-      </c>
-      <c r="C67" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="D67">
-        <v>18.72</v>
-      </c>
-      <c r="F67">
-        <v>5</v>
-      </c>
-      <c r="G67" s="2" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="68" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A68" s="8" t="s">
-        <v>149</v>
-      </c>
-      <c r="B68" s="8" t="s">
-        <v>190</v>
-      </c>
-      <c r="C68" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="D68">
-        <v>30</v>
-      </c>
-      <c r="F68">
-        <v>5</v>
-      </c>
-      <c r="G68" s="2" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="69" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A69" s="8" t="s">
-        <v>150</v>
-      </c>
-      <c r="B69" s="8" t="s">
-        <v>191</v>
-      </c>
-      <c r="C69" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="D69">
-        <v>24.479999999999997</v>
-      </c>
-      <c r="F69">
-        <v>5</v>
-      </c>
-      <c r="G69" s="2" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="70" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A70" s="8" t="s">
-        <v>151</v>
-      </c>
-      <c r="B70" s="8" t="s">
-        <v>192</v>
-      </c>
-      <c r="C70" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="D70">
-        <v>90</v>
-      </c>
-      <c r="F70">
-        <v>5</v>
-      </c>
-      <c r="G70" s="2" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="71" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A71" s="8" t="s">
-        <v>241</v>
-      </c>
-      <c r="B71" s="8" t="s">
-        <v>237</v>
-      </c>
-      <c r="G71" s="2" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="72" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A72" s="8" t="s">
-        <v>239</v>
-      </c>
-      <c r="B72" s="8" t="s">
-        <v>233</v>
-      </c>
-      <c r="G72" s="2" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="73" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A73" s="8" t="s">
-        <v>240</v>
-      </c>
-      <c r="B73" s="8" t="s">
-        <v>234</v>
-      </c>
-      <c r="G73" s="2" t="s">
-        <v>236</v>
       </c>
     </row>
   </sheetData>

--- a/urunler.xlsx
+++ b/urunler.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\Githup\portal\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A22F93D-30BF-4483-9077-C28E52F98476}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58E51CC3-916E-40EB-BBD2-A85CFE2A21A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -738,8 +738,8 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="3">
     <numFmt numFmtId="44" formatCode="_-&quot;₺&quot;* #,##0.00_-;\-&quot;₺&quot;* #,##0.00_-;_-&quot;₺&quot;* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="165" formatCode="_-[$€-2]\ * #,##0.00_-;\-[$€-2]\ * #,##0.00_-;_-[$€-2]\ * &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="166" formatCode="_-[$₺-41F]* #,##0.00_-;\-[$₺-41F]* #,##0.00_-;_-[$₺-41F]* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="165" formatCode="_-[$₺-41F]* #,##0.00_-;\-[$₺-41F]* #,##0.00_-;_-[$₺-41F]* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="166" formatCode="_-* #,##0.00\ [$€-1]_-;\-* #,##0.00\ [$€-1]_-;_-* &quot;-&quot;??\ [$€-1]_-;_-@_-"/>
   </numFmts>
   <fonts count="6" x14ac:knownFonts="1">
     <font>
@@ -819,14 +819,14 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1086,7 +1086,7 @@
       <c r="C2" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="D2" s="9">
+      <c r="D2" s="11">
         <v>152</v>
       </c>
       <c r="E2" s="3"/>
@@ -1107,7 +1107,7 @@
       <c r="C3" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="D3" s="9">
+      <c r="D3" s="11">
         <v>175</v>
       </c>
       <c r="E3" s="3"/>
@@ -1128,7 +1128,7 @@
       <c r="C4" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="D4" s="10">
+      <c r="D4" s="12">
         <v>191</v>
       </c>
       <c r="E4" s="2"/>
@@ -1149,7 +1149,7 @@
       <c r="C5" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="D5" s="10">
+      <c r="D5" s="12">
         <v>216</v>
       </c>
       <c r="E5" s="2"/>
@@ -1168,7 +1168,7 @@
       <c r="C6" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="D6" s="10">
+      <c r="D6" s="12">
         <v>256</v>
       </c>
       <c r="E6" s="2"/>
@@ -1189,7 +1189,7 @@
       <c r="C7" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="D7" s="10">
+      <c r="D7" s="12">
         <v>81</v>
       </c>
       <c r="E7" s="2"/>
@@ -1210,7 +1210,7 @@
       <c r="C8" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="D8" s="10">
+      <c r="D8" s="12">
         <v>136</v>
       </c>
       <c r="E8" s="2"/>
@@ -1231,7 +1231,7 @@
       <c r="C9" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="D9" s="10">
+      <c r="D9" s="12">
         <v>98</v>
       </c>
       <c r="E9" s="2"/>
@@ -1252,7 +1252,7 @@
       <c r="C10" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="D10" s="10">
+      <c r="D10" s="12">
         <v>116</v>
       </c>
       <c r="E10" s="2"/>
@@ -1273,7 +1273,7 @@
       <c r="C11" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="D11" s="10">
+      <c r="D11" s="12">
         <v>122</v>
       </c>
       <c r="E11" s="2"/>
@@ -1294,7 +1294,7 @@
       <c r="C12" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="D12" s="11">
+      <c r="D12" s="9">
         <v>6480.92</v>
       </c>
       <c r="F12">
@@ -1314,7 +1314,7 @@
       <c r="C13" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="D13" s="11">
+      <c r="D13" s="9">
         <v>8841.6200000000008</v>
       </c>
       <c r="F13">
@@ -1334,7 +1334,7 @@
       <c r="C14" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="D14" s="11">
+      <c r="D14" s="9">
         <v>8520.89</v>
       </c>
       <c r="F14">
@@ -1354,7 +1354,7 @@
       <c r="C15" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="D15" s="11">
+      <c r="D15" s="9">
         <v>9540.83</v>
       </c>
       <c r="F15">
@@ -1374,7 +1374,7 @@
       <c r="C16" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="D16" s="11">
+      <c r="D16" s="9">
         <v>7620.91</v>
       </c>
       <c r="F16">
@@ -1394,7 +1394,7 @@
       <c r="C17" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="D17" s="11">
+      <c r="D17" s="9">
         <v>2577.54</v>
       </c>
       <c r="F17">
@@ -1414,7 +1414,7 @@
       <c r="C18" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="D18" s="11">
+      <c r="D18" s="9">
         <v>2550.75</v>
       </c>
       <c r="F18">
@@ -1434,7 +1434,7 @@
       <c r="C19" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="D19" s="11">
+      <c r="D19" s="9">
         <v>3226.53</v>
       </c>
       <c r="F19">
@@ -1454,7 +1454,7 @@
       <c r="C20" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="D20" s="11">
+      <c r="D20" s="9">
         <v>3611.43</v>
       </c>
       <c r="F20">
@@ -1474,7 +1474,7 @@
       <c r="C21" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="D21" s="11">
+      <c r="D21" s="9">
         <v>3828.73</v>
       </c>
       <c r="F21">
@@ -1494,7 +1494,7 @@
       <c r="C22" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="D22" s="11">
+      <c r="D22" s="9">
         <v>4020.83</v>
       </c>
       <c r="F22">
@@ -1514,7 +1514,7 @@
       <c r="C23" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="D23" s="11">
+      <c r="D23" s="9">
         <v>4020.91</v>
       </c>
       <c r="F23">
@@ -1534,7 +1534,7 @@
       <c r="C24" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="D24" s="11">
+      <c r="D24" s="9">
         <v>4386.92</v>
       </c>
       <c r="F24">
@@ -1554,7 +1554,7 @@
       <c r="C25" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="D25" s="12">
+      <c r="D25" s="10">
         <v>728.72</v>
       </c>
       <c r="F25">
@@ -1574,7 +1574,7 @@
       <c r="C26" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="D26" s="12">
+      <c r="D26" s="10">
         <v>474.36</v>
       </c>
       <c r="F26">
@@ -1594,7 +1594,7 @@
       <c r="C27" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="D27" s="12">
+      <c r="D27" s="10">
         <v>522.48</v>
       </c>
       <c r="F27">
@@ -1614,7 +1614,7 @@
       <c r="C28" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="D28" s="12">
+      <c r="D28" s="10">
         <v>653.98</v>
       </c>
       <c r="F28">
@@ -1634,7 +1634,7 @@
       <c r="C29" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="D29" s="12">
+      <c r="D29" s="10">
         <v>172.59</v>
       </c>
       <c r="F29">
@@ -1654,7 +1654,7 @@
       <c r="C30" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="D30" s="12">
+      <c r="D30" s="10">
         <v>172.59</v>
       </c>
       <c r="F30">
@@ -1674,7 +1674,7 @@
       <c r="C31" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="D31" s="12">
+      <c r="D31" s="10">
         <v>21.69</v>
       </c>
       <c r="F31">
@@ -1694,7 +1694,7 @@
       <c r="C32" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="D32" s="12">
+      <c r="D32" s="10">
         <v>198.99</v>
       </c>
       <c r="F32">
@@ -1714,7 +1714,7 @@
       <c r="C33" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="D33" s="12">
+      <c r="D33" s="10">
         <v>144.99</v>
       </c>
       <c r="F33">
@@ -1734,7 +1734,7 @@
       <c r="C34" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="D34" s="12">
+      <c r="D34" s="10">
         <v>42.99</v>
       </c>
       <c r="F34">
@@ -1754,7 +1754,7 @@
       <c r="C35" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="D35" s="12">
+      <c r="D35" s="10">
         <v>165</v>
       </c>
       <c r="F35">
@@ -1774,7 +1774,7 @@
       <c r="C36" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="D36" s="12">
+      <c r="D36" s="10">
         <v>24</v>
       </c>
       <c r="F36">
@@ -1794,7 +1794,7 @@
       <c r="C37" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="D37" s="12">
+      <c r="D37" s="10">
         <v>168</v>
       </c>
       <c r="F37">
@@ -1814,7 +1814,7 @@
       <c r="C38" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="D38" s="12">
+      <c r="D38" s="10">
         <v>150</v>
       </c>
       <c r="F38">
@@ -1834,7 +1834,7 @@
       <c r="C39" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="D39" s="12">
+      <c r="D39" s="10">
         <v>179.4</v>
       </c>
       <c r="F39">
@@ -1854,7 +1854,7 @@
       <c r="C40" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="D40" s="12">
+      <c r="D40" s="10">
         <v>300</v>
       </c>
       <c r="F40">
@@ -1874,7 +1874,7 @@
       <c r="C41" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="D41" s="12">
+      <c r="D41" s="10">
         <v>225</v>
       </c>
       <c r="F41">
@@ -1894,7 +1894,7 @@
       <c r="C42" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="D42" s="12">
+      <c r="D42" s="10">
         <v>129.99599999999998</v>
       </c>
       <c r="F42">
@@ -1914,7 +1914,7 @@
       <c r="C43" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="D43" s="12">
+      <c r="D43" s="10">
         <v>300</v>
       </c>
       <c r="F43">
@@ -1934,7 +1934,7 @@
       <c r="C44" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="D44" s="12">
+      <c r="D44" s="10">
         <v>10.38</v>
       </c>
       <c r="F44">
@@ -1954,7 +1954,7 @@
       <c r="C45" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="D45" s="12">
+      <c r="D45" s="10">
         <v>52.8</v>
       </c>
       <c r="F45">
@@ -1974,7 +1974,7 @@
       <c r="C46" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="D46" s="12">
+      <c r="D46" s="10">
         <v>255</v>
       </c>
       <c r="F46">
@@ -1994,7 +1994,7 @@
       <c r="C47" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="D47" s="12">
+      <c r="D47" s="10">
         <v>39</v>
       </c>
       <c r="F47">
@@ -2014,7 +2014,7 @@
       <c r="C48" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="D48" s="12">
+      <c r="D48" s="10">
         <v>128.4</v>
       </c>
       <c r="F48">
@@ -2034,7 +2034,7 @@
       <c r="C49" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="D49" s="12">
+      <c r="D49" s="10">
         <v>127.19999999999999</v>
       </c>
       <c r="F49">
@@ -2054,7 +2054,7 @@
       <c r="C50" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="D50" s="12">
+      <c r="D50" s="10">
         <v>225</v>
       </c>
       <c r="F50">
@@ -2074,7 +2074,7 @@
       <c r="C51" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="D51" s="12">
+      <c r="D51" s="10">
         <v>180</v>
       </c>
       <c r="F51">
@@ -2094,7 +2094,7 @@
       <c r="C52" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="D52" s="12">
+      <c r="D52" s="10">
         <v>26.255999999999997</v>
       </c>
       <c r="F52">
@@ -2114,7 +2114,7 @@
       <c r="C53" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="D53" s="12">
+      <c r="D53" s="10">
         <v>202.79999999999998</v>
       </c>
       <c r="F53">
@@ -2134,7 +2134,7 @@
       <c r="C54" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="D54" s="12">
+      <c r="D54" s="10">
         <v>13.56</v>
       </c>
       <c r="F54">
@@ -2154,7 +2154,7 @@
       <c r="C55" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="D55" s="12">
+      <c r="D55" s="10">
         <v>127.19999999999999</v>
       </c>
       <c r="F55">
@@ -2174,7 +2174,7 @@
       <c r="C56" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="D56" s="12">
+      <c r="D56" s="10">
         <v>150</v>
       </c>
       <c r="F56">
@@ -2194,7 +2194,7 @@
       <c r="C57" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="D57" s="12">
+      <c r="D57" s="10">
         <v>156</v>
       </c>
       <c r="F57">
@@ -2214,7 +2214,7 @@
       <c r="C58" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="D58" s="12">
+      <c r="D58" s="10">
         <v>216</v>
       </c>
       <c r="F58">
@@ -2234,7 +2234,7 @@
       <c r="C59" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="D59" s="12">
+      <c r="D59" s="10">
         <v>90</v>
       </c>
       <c r="F59">
@@ -2254,7 +2254,7 @@
       <c r="C60" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="D60" s="12">
+      <c r="D60" s="10">
         <v>127.19999999999999</v>
       </c>
       <c r="F60">
@@ -2274,7 +2274,7 @@
       <c r="C61" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="D61" s="12">
+      <c r="D61" s="10">
         <v>144</v>
       </c>
       <c r="F61">
@@ -2294,7 +2294,7 @@
       <c r="C62" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="D62" s="12">
+      <c r="D62" s="10">
         <v>75.599999999999994</v>
       </c>
       <c r="F62">
@@ -2314,7 +2314,7 @@
       <c r="C63" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="D63" s="12">
+      <c r="D63" s="10">
         <v>194.4</v>
       </c>
       <c r="F63">
@@ -2334,7 +2334,7 @@
       <c r="C64" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="D64" s="12">
+      <c r="D64" s="10">
         <v>285</v>
       </c>
       <c r="F64">
@@ -2354,7 +2354,7 @@
       <c r="C65" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="D65" s="12">
+      <c r="D65" s="10">
         <v>18.72</v>
       </c>
       <c r="F65">
@@ -2374,7 +2374,7 @@
       <c r="C66" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="D66" s="12">
+      <c r="D66" s="10">
         <v>30</v>
       </c>
       <c r="F66">
@@ -2394,7 +2394,7 @@
       <c r="C67" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="D67" s="12">
+      <c r="D67" s="10">
         <v>24.479999999999997</v>
       </c>
       <c r="F67">
@@ -2414,7 +2414,7 @@
       <c r="C68" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="D68" s="12">
+      <c r="D68" s="10">
         <v>90</v>
       </c>
       <c r="F68">

--- a/urunler.xlsx
+++ b/urunler.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\Githup\portal\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58E51CC3-916E-40EB-BBD2-A85CFE2A21A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DCCDA109-E5A0-4AF7-A251-33784D14BBE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -738,8 +738,8 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="3">
     <numFmt numFmtId="44" formatCode="_-&quot;₺&quot;* #,##0.00_-;\-&quot;₺&quot;* #,##0.00_-;_-&quot;₺&quot;* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="165" formatCode="_-[$₺-41F]* #,##0.00_-;\-[$₺-41F]* #,##0.00_-;_-[$₺-41F]* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="166" formatCode="_-* #,##0.00\ [$€-1]_-;\-* #,##0.00\ [$€-1]_-;_-* &quot;-&quot;??\ [$€-1]_-;_-@_-"/>
+    <numFmt numFmtId="164" formatCode="_-[$₺-41F]* #,##0.00_-;\-[$₺-41F]* #,##0.00_-;_-[$₺-41F]* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="165" formatCode="_-* #,##0.00\ [$€-1]_-;\-* #,##0.00\ [$€-1]_-;_-* &quot;-&quot;??\ [$€-1]_-;_-@_-"/>
   </numFmts>
   <fonts count="6" x14ac:knownFonts="1">
     <font>
@@ -819,12 +819,12 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellXfs>

--- a/urunler.xlsx
+++ b/urunler.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\Githup\portal\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DCCDA109-E5A0-4AF7-A251-33784D14BBE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C075B78-8C34-48CE-9801-46E087263FB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -738,8 +738,8 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="3">
     <numFmt numFmtId="44" formatCode="_-&quot;₺&quot;* #,##0.00_-;\-&quot;₺&quot;* #,##0.00_-;_-&quot;₺&quot;* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="164" formatCode="_-[$₺-41F]* #,##0.00_-;\-[$₺-41F]* #,##0.00_-;_-[$₺-41F]* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="165" formatCode="_-* #,##0.00\ [$€-1]_-;\-* #,##0.00\ [$€-1]_-;_-* &quot;-&quot;??\ [$€-1]_-;_-@_-"/>
+    <numFmt numFmtId="167" formatCode="[$₺-41F]#,##0.00;[Red][$₺-41F]#,##0.00"/>
+    <numFmt numFmtId="168" formatCode="[$€-2]\ #,##0.00;[Red][$€-2]\ #,##0.00"/>
   </numFmts>
   <fonts count="6" x14ac:knownFonts="1">
     <font>
@@ -819,14 +819,10 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="168" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="168" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>

--- a/urunler.xlsx
+++ b/urunler.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\Githup\portal\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C075B78-8C34-48CE-9801-46E087263FB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE8A1834-5535-48A6-A5D3-818E4D777502}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="301" uniqueCount="232">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="709" uniqueCount="235">
   <si>
     <t>urun_no</t>
   </si>
@@ -730,6 +730,15 @@
   </si>
   <si>
     <t>REKLAM3</t>
+  </si>
+  <si>
+    <t>para_birimi</t>
+  </si>
+  <si>
+    <t>EURO</t>
+  </si>
+  <si>
+    <t>TL</t>
   </si>
 </sst>
 </file>
@@ -738,8 +747,8 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="3">
     <numFmt numFmtId="44" formatCode="_-&quot;₺&quot;* #,##0.00_-;\-&quot;₺&quot;* #,##0.00_-;_-&quot;₺&quot;* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="167" formatCode="[$₺-41F]#,##0.00;[Red][$₺-41F]#,##0.00"/>
-    <numFmt numFmtId="168" formatCode="[$€-2]\ #,##0.00;[Red][$€-2]\ #,##0.00"/>
+    <numFmt numFmtId="164" formatCode="[$₺-41F]#,##0.00;[Red][$₺-41F]#,##0.00"/>
+    <numFmt numFmtId="165" formatCode="[$€-2]\ #,##0.00;[Red][$€-2]\ #,##0.00"/>
   </numFmts>
   <fonts count="6" x14ac:knownFonts="1">
     <font>
@@ -819,10 +828,10 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="167" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="168" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="168" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1042,14 +1051,14 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:G71"/>
+  <dimension ref="A1:H71"/>
   <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="41.140625" customWidth="1"/>
     <col min="9" max="15" width="12.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1071,8 +1080,11 @@
       <c r="G1" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="2" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="H1" s="1" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A2" s="7">
         <v>56001</v>
       </c>
@@ -1092,8 +1104,11 @@
       <c r="G2" s="4" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="3" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="H2" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A3" s="7">
         <v>57001</v>
       </c>
@@ -1113,8 +1128,11 @@
       <c r="G3" s="4" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="4" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H3" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="8">
         <v>58001</v>
       </c>
@@ -1134,8 +1152,11 @@
       <c r="G4" s="2" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="5" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H4" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="8">
         <v>59502</v>
       </c>
@@ -1153,8 +1174,11 @@
       <c r="G5" s="2" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="6" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H5" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="8">
         <v>60501</v>
       </c>
@@ -1174,8 +1198,11 @@
       <c r="G6" s="2" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="7" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H6" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="8">
         <v>56009</v>
       </c>
@@ -1195,8 +1222,11 @@
       <c r="G7" s="2" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="8" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H7" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="8">
         <v>57011</v>
       </c>
@@ -1216,8 +1246,11 @@
       <c r="G8" s="2" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="9" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H8" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="8">
         <v>57044</v>
       </c>
@@ -1237,8 +1270,11 @@
       <c r="G9" s="2" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="10" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H9" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="8">
         <v>58014</v>
       </c>
@@ -1258,8 +1294,11 @@
       <c r="G10" s="2" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="11" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H10" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="8">
         <v>59533</v>
       </c>
@@ -1279,8 +1318,11 @@
       <c r="G11" s="2" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="12" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H11" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>56</v>
       </c>
@@ -1299,8 +1341,11 @@
       <c r="G12" s="2" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="13" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H12" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>57</v>
       </c>
@@ -1319,8 +1364,11 @@
       <c r="G13" s="2" t="s">
         <v>80</v>
       </c>
-    </row>
-    <row r="14" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H13" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>58</v>
       </c>
@@ -1339,8 +1387,11 @@
       <c r="G14" s="2" t="s">
         <v>81</v>
       </c>
-    </row>
-    <row r="15" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H14" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>59</v>
       </c>
@@ -1359,8 +1410,11 @@
       <c r="G15" s="2" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="16" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H15" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>57</v>
       </c>
@@ -1379,8 +1433,11 @@
       <c r="G16" s="2" t="s">
         <v>80</v>
       </c>
-    </row>
-    <row r="17" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H16" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>60</v>
       </c>
@@ -1399,8 +1456,11 @@
       <c r="G17" s="2" t="s">
         <v>83</v>
       </c>
-    </row>
-    <row r="18" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H17" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>61</v>
       </c>
@@ -1419,8 +1479,11 @@
       <c r="G18" s="2" t="s">
         <v>84</v>
       </c>
-    </row>
-    <row r="19" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H18" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>62</v>
       </c>
@@ -1439,8 +1502,11 @@
       <c r="G19" s="2" t="s">
         <v>85</v>
       </c>
-    </row>
-    <row r="20" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H19" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>56</v>
       </c>
@@ -1459,8 +1525,11 @@
       <c r="G20" s="2" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="21" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H20" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>57</v>
       </c>
@@ -1479,8 +1548,11 @@
       <c r="G21" s="2" t="s">
         <v>80</v>
       </c>
-    </row>
-    <row r="22" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H21" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>63</v>
       </c>
@@ -1499,8 +1571,11 @@
       <c r="G22" s="2" t="s">
         <v>86</v>
       </c>
-    </row>
-    <row r="23" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H22" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>64</v>
       </c>
@@ -1519,8 +1594,11 @@
       <c r="G23" s="2" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="24" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H23" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="5">
         <v>10089</v>
       </c>
@@ -1539,8 +1617,11 @@
       <c r="G24" s="2" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="25" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H24" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="2" t="s">
         <v>94</v>
       </c>
@@ -1559,8 +1640,11 @@
       <c r="G25" s="2" t="s">
         <v>98</v>
       </c>
-    </row>
-    <row r="26" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H25" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="2" t="s">
         <v>95</v>
       </c>
@@ -1579,8 +1663,11 @@
       <c r="G26" s="2" t="s">
         <v>99</v>
       </c>
-    </row>
-    <row r="27" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H26" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="2" t="s">
         <v>96</v>
       </c>
@@ -1599,8 +1686,11 @@
       <c r="G27" s="2" t="s">
         <v>100</v>
       </c>
-    </row>
-    <row r="28" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H27" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="2" t="s">
         <v>97</v>
       </c>
@@ -1619,8 +1709,11 @@
       <c r="G28" s="2" t="s">
         <v>101</v>
       </c>
-    </row>
-    <row r="29" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H28" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="6" t="s">
         <v>102</v>
       </c>
@@ -1639,8 +1732,11 @@
       <c r="G29" s="2" t="s">
         <v>183</v>
       </c>
-    </row>
-    <row r="30" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H29" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="6" t="s">
         <v>103</v>
       </c>
@@ -1659,8 +1755,11 @@
       <c r="G30" s="2" t="s">
         <v>184</v>
       </c>
-    </row>
-    <row r="31" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H30" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="6" t="s">
         <v>104</v>
       </c>
@@ -1679,8 +1778,11 @@
       <c r="G31" s="2" t="s">
         <v>185</v>
       </c>
-    </row>
-    <row r="32" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H31" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="6" t="s">
         <v>105</v>
       </c>
@@ -1699,8 +1801,11 @@
       <c r="G32" s="2" t="s">
         <v>186</v>
       </c>
-    </row>
-    <row r="33" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H32" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="6" t="s">
         <v>106</v>
       </c>
@@ -1719,8 +1824,11 @@
       <c r="G33" s="2" t="s">
         <v>187</v>
       </c>
-    </row>
-    <row r="34" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H33" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="6" t="s">
         <v>107</v>
       </c>
@@ -1739,8 +1847,11 @@
       <c r="G34" s="2" t="s">
         <v>188</v>
       </c>
-    </row>
-    <row r="35" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H34" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="6" t="s">
         <v>108</v>
       </c>
@@ -1759,8 +1870,11 @@
       <c r="G35" s="2" t="s">
         <v>189</v>
       </c>
-    </row>
-    <row r="36" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H35" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="6" t="s">
         <v>109</v>
       </c>
@@ -1779,8 +1893,11 @@
       <c r="G36" s="2" t="s">
         <v>190</v>
       </c>
-    </row>
-    <row r="37" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H36" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="6" t="s">
         <v>110</v>
       </c>
@@ -1799,8 +1916,11 @@
       <c r="G37" s="2" t="s">
         <v>191</v>
       </c>
-    </row>
-    <row r="38" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H37" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="6" t="s">
         <v>111</v>
       </c>
@@ -1819,8 +1939,11 @@
       <c r="G38" s="2" t="s">
         <v>192</v>
       </c>
-    </row>
-    <row r="39" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H38" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="6" t="s">
         <v>112</v>
       </c>
@@ -1839,8 +1962,11 @@
       <c r="G39" s="2" t="s">
         <v>193</v>
       </c>
-    </row>
-    <row r="40" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H39" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="6" t="s">
         <v>113</v>
       </c>
@@ -1859,8 +1985,11 @@
       <c r="G40" s="2" t="s">
         <v>194</v>
       </c>
-    </row>
-    <row r="41" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H40" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="6" t="s">
         <v>114</v>
       </c>
@@ -1879,8 +2008,11 @@
       <c r="G41" s="2" t="s">
         <v>195</v>
       </c>
-    </row>
-    <row r="42" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H41" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="6" t="s">
         <v>115</v>
       </c>
@@ -1899,8 +2031,11 @@
       <c r="G42" s="2" t="s">
         <v>196</v>
       </c>
-    </row>
-    <row r="43" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H42" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="6" t="s">
         <v>116</v>
       </c>
@@ -1919,8 +2054,11 @@
       <c r="G43" s="2" t="s">
         <v>197</v>
       </c>
-    </row>
-    <row r="44" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H43" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="6" t="s">
         <v>117</v>
       </c>
@@ -1939,8 +2077,11 @@
       <c r="G44" s="2" t="s">
         <v>198</v>
       </c>
-    </row>
-    <row r="45" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H44" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="6" t="s">
         <v>118</v>
       </c>
@@ -1959,8 +2100,11 @@
       <c r="G45" s="2" t="s">
         <v>199</v>
       </c>
-    </row>
-    <row r="46" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H45" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="6" t="s">
         <v>119</v>
       </c>
@@ -1979,8 +2123,11 @@
       <c r="G46" s="2" t="s">
         <v>200</v>
       </c>
-    </row>
-    <row r="47" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H46" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="6" t="s">
         <v>120</v>
       </c>
@@ -1999,8 +2146,11 @@
       <c r="G47" s="2" t="s">
         <v>201</v>
       </c>
-    </row>
-    <row r="48" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H47" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="6" t="s">
         <v>121</v>
       </c>
@@ -2019,8 +2169,11 @@
       <c r="G48" s="2" t="s">
         <v>202</v>
       </c>
-    </row>
-    <row r="49" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H48" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="6" t="s">
         <v>122</v>
       </c>
@@ -2039,8 +2192,11 @@
       <c r="G49" s="2" t="s">
         <v>203</v>
       </c>
-    </row>
-    <row r="50" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H49" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="6" t="s">
         <v>123</v>
       </c>
@@ -2059,8 +2215,11 @@
       <c r="G50" s="2" t="s">
         <v>204</v>
       </c>
-    </row>
-    <row r="51" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H50" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="6" t="s">
         <v>124</v>
       </c>
@@ -2079,8 +2238,11 @@
       <c r="G51" s="2" t="s">
         <v>205</v>
       </c>
-    </row>
-    <row r="52" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H51" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="6" t="s">
         <v>125</v>
       </c>
@@ -2099,8 +2261,11 @@
       <c r="G52" s="2" t="s">
         <v>206</v>
       </c>
-    </row>
-    <row r="53" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H52" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="6" t="s">
         <v>126</v>
       </c>
@@ -2119,8 +2284,11 @@
       <c r="G53" s="2" t="s">
         <v>207</v>
       </c>
-    </row>
-    <row r="54" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H53" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="6" t="s">
         <v>127</v>
       </c>
@@ -2139,8 +2307,11 @@
       <c r="G54" s="2" t="s">
         <v>208</v>
       </c>
-    </row>
-    <row r="55" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H54" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="6" t="s">
         <v>128</v>
       </c>
@@ -2159,8 +2330,11 @@
       <c r="G55" s="2" t="s">
         <v>209</v>
       </c>
-    </row>
-    <row r="56" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H55" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="6" t="s">
         <v>129</v>
       </c>
@@ -2179,8 +2353,11 @@
       <c r="G56" s="2" t="s">
         <v>210</v>
       </c>
-    </row>
-    <row r="57" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H56" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="6" t="s">
         <v>130</v>
       </c>
@@ -2199,8 +2376,11 @@
       <c r="G57" s="2" t="s">
         <v>211</v>
       </c>
-    </row>
-    <row r="58" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H57" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="6" t="s">
         <v>131</v>
       </c>
@@ -2219,8 +2399,11 @@
       <c r="G58" s="2" t="s">
         <v>212</v>
       </c>
-    </row>
-    <row r="59" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H58" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="6" t="s">
         <v>132</v>
       </c>
@@ -2239,8 +2422,11 @@
       <c r="G59" s="2" t="s">
         <v>213</v>
       </c>
-    </row>
-    <row r="60" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H59" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60" s="6" t="s">
         <v>133</v>
       </c>
@@ -2259,8 +2445,11 @@
       <c r="G60" s="2" t="s">
         <v>214</v>
       </c>
-    </row>
-    <row r="61" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H60" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="6" t="s">
         <v>134</v>
       </c>
@@ -2279,8 +2468,11 @@
       <c r="G61" s="2" t="s">
         <v>215</v>
       </c>
-    </row>
-    <row r="62" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H61" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="6" t="s">
         <v>135</v>
       </c>
@@ -2299,8 +2491,11 @@
       <c r="G62" s="2" t="s">
         <v>216</v>
       </c>
-    </row>
-    <row r="63" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H62" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A63" s="6" t="s">
         <v>136</v>
       </c>
@@ -2319,8 +2514,11 @@
       <c r="G63" s="2" t="s">
         <v>217</v>
       </c>
-    </row>
-    <row r="64" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H63" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A64" s="6" t="s">
         <v>137</v>
       </c>
@@ -2339,8 +2537,11 @@
       <c r="G64" s="2" t="s">
         <v>218</v>
       </c>
-    </row>
-    <row r="65" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H64" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" s="6" t="s">
         <v>138</v>
       </c>
@@ -2359,8 +2560,11 @@
       <c r="G65" s="2" t="s">
         <v>219</v>
       </c>
-    </row>
-    <row r="66" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H65" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A66" s="6" t="s">
         <v>139</v>
       </c>
@@ -2379,8 +2583,11 @@
       <c r="G66" s="2" t="s">
         <v>220</v>
       </c>
-    </row>
-    <row r="67" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H66" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A67" s="6" t="s">
         <v>140</v>
       </c>
@@ -2399,8 +2606,11 @@
       <c r="G67" s="2" t="s">
         <v>221</v>
       </c>
-    </row>
-    <row r="68" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H67" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A68" s="6" t="s">
         <v>141</v>
       </c>
@@ -2419,8 +2629,11 @@
       <c r="G68" s="2" t="s">
         <v>222</v>
       </c>
-    </row>
-    <row r="69" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H68" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A69" s="6" t="s">
         <v>231</v>
       </c>
@@ -2431,7 +2644,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="70" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A70" s="6" t="s">
         <v>229</v>
       </c>
@@ -2442,7 +2655,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="71" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A71" s="6" t="s">
         <v>230</v>
       </c>

--- a/urunler.xlsx
+++ b/urunler.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\Githup\portal\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE8A1834-5535-48A6-A5D3-818E4D777502}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC59056E-9F5E-43F9-8716-BD8CA33C78A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="709" uniqueCount="235">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="369" uniqueCount="235">
   <si>
     <t>urun_no</t>
   </si>

--- a/urunler.xlsx
+++ b/urunler.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\Githup\portal\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC59056E-9F5E-43F9-8716-BD8CA33C78A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0BA7D349-12A6-4735-AAA6-3341499A3732}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1450,9 +1450,6 @@
       <c r="D17" s="9">
         <v>2577.54</v>
       </c>
-      <c r="F17">
-        <v>5</v>
-      </c>
       <c r="G17" s="2" t="s">
         <v>83</v>
       </c>
@@ -1841,9 +1838,6 @@
       <c r="D34" s="10">
         <v>42.99</v>
       </c>
-      <c r="F34">
-        <v>5</v>
-      </c>
       <c r="G34" s="2" t="s">
         <v>188</v>
       </c>
@@ -1933,9 +1927,6 @@
       <c r="D38" s="10">
         <v>150</v>
       </c>
-      <c r="F38">
-        <v>5</v>
-      </c>
       <c r="G38" s="2" t="s">
         <v>192</v>
       </c>
@@ -2071,9 +2062,6 @@
       <c r="D44" s="10">
         <v>10.38</v>
       </c>
-      <c r="F44">
-        <v>5</v>
-      </c>
       <c r="G44" s="2" t="s">
         <v>198</v>
       </c>
@@ -2140,9 +2128,6 @@
       <c r="D47" s="10">
         <v>39</v>
       </c>
-      <c r="F47">
-        <v>5</v>
-      </c>
       <c r="G47" s="2" t="s">
         <v>201</v>
       </c>
@@ -2209,9 +2194,6 @@
       <c r="D50" s="10">
         <v>225</v>
       </c>
-      <c r="F50">
-        <v>5</v>
-      </c>
       <c r="G50" s="2" t="s">
         <v>204</v>
       </c>
@@ -2255,9 +2237,6 @@
       <c r="D52" s="10">
         <v>26.255999999999997</v>
       </c>
-      <c r="F52">
-        <v>5</v>
-      </c>
       <c r="G52" s="2" t="s">
         <v>206</v>
       </c>
@@ -2301,9 +2280,6 @@
       <c r="D54" s="10">
         <v>13.56</v>
       </c>
-      <c r="F54">
-        <v>5</v>
-      </c>
       <c r="G54" s="2" t="s">
         <v>208</v>
       </c>
@@ -2347,9 +2323,6 @@
       <c r="D56" s="10">
         <v>150</v>
       </c>
-      <c r="F56">
-        <v>5</v>
-      </c>
       <c r="G56" s="2" t="s">
         <v>210</v>
       </c>
@@ -2393,9 +2366,6 @@
       <c r="D58" s="10">
         <v>216</v>
       </c>
-      <c r="F58">
-        <v>5</v>
-      </c>
       <c r="G58" s="2" t="s">
         <v>212</v>
       </c>
@@ -2416,9 +2386,6 @@
       <c r="D59" s="10">
         <v>90</v>
       </c>
-      <c r="F59">
-        <v>5</v>
-      </c>
       <c r="G59" s="2" t="s">
         <v>213</v>
       </c>
@@ -2439,9 +2406,6 @@
       <c r="D60" s="10">
         <v>127.19999999999999</v>
       </c>
-      <c r="F60">
-        <v>5</v>
-      </c>
       <c r="G60" s="2" t="s">
         <v>214</v>
       </c>
@@ -2485,9 +2449,6 @@
       <c r="D62" s="10">
         <v>75.599999999999994</v>
       </c>
-      <c r="F62">
-        <v>5</v>
-      </c>
       <c r="G62" s="2" t="s">
         <v>216</v>
       </c>
@@ -2554,9 +2515,6 @@
       <c r="D65" s="10">
         <v>18.72</v>
       </c>
-      <c r="F65">
-        <v>5</v>
-      </c>
       <c r="G65" s="2" t="s">
         <v>219</v>
       </c>
@@ -2577,9 +2535,6 @@
       <c r="D66" s="10">
         <v>30</v>
       </c>
-      <c r="F66">
-        <v>5</v>
-      </c>
       <c r="G66" s="2" t="s">
         <v>220</v>
       </c>
@@ -2600,9 +2555,6 @@
       <c r="D67" s="10">
         <v>24.479999999999997</v>
       </c>
-      <c r="F67">
-        <v>5</v>
-      </c>
       <c r="G67" s="2" t="s">
         <v>221</v>
       </c>
@@ -2622,9 +2574,6 @@
       </c>
       <c r="D68" s="10">
         <v>90</v>
-      </c>
-      <c r="F68">
-        <v>5</v>
       </c>
       <c r="G68" s="2" t="s">
         <v>222</v>

--- a/urunler.xlsx
+++ b/urunler.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\Githup\portal\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{290D0C62-A2E7-4DC0-B085-411ED975833A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3BB1784B-82D9-4858-8627-78FD3BD32162}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/urunler.xlsx
+++ b/urunler.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\Githup\portal\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3BB1784B-82D9-4858-8627-78FD3BD32162}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{990E353C-7A25-4C81-8FE8-506690A25088}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -865,17 +865,23 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <family val="2"/>
+      <charset val="162"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
+      <family val="2"/>
+      <charset val="162"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="8"/>
       <name val="Arial"/>
+      <family val="2"/>
+      <charset val="162"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1470,6 +1476,9 @@
       <c r="D15" s="7">
         <v>8520.89</v>
       </c>
+      <c r="E15">
+        <v>5</v>
+      </c>
       <c r="F15">
         <v>50</v>
       </c>

--- a/urunler.xlsx
+++ b/urunler.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\Githup\portal\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{990E353C-7A25-4C81-8FE8-506690A25088}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78B704A1-28FC-417D-BFE0-BADB106FD471}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -923,7 +923,7 @@
     <xf numFmtId="44" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -945,6 +945,7 @@
     <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="2"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="2" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1165,7 +1166,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:H83"/>
+  <dimension ref="A1:I83"/>
   <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="57.7109375" customWidth="1"/>
@@ -1174,7 +1175,7 @@
     <col min="9" max="15" width="12.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1200,7 +1201,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A2" s="5">
         <v>56001</v>
       </c>
@@ -1211,7 +1212,7 @@
         <v>45</v>
       </c>
       <c r="D2" s="12">
-        <v>152</v>
+        <v>140.75</v>
       </c>
       <c r="E2" s="3"/>
       <c r="F2" s="1">
@@ -1220,8 +1221,9 @@
       <c r="G2" s="4" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="3" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="I2" s="15"/>
+    </row>
+    <row r="3" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A3" s="5">
         <v>57001</v>
       </c>
@@ -1232,7 +1234,7 @@
         <v>45</v>
       </c>
       <c r="D3" s="12">
-        <v>175</v>
+        <v>162.76</v>
       </c>
       <c r="E3" s="3"/>
       <c r="F3" s="1">
@@ -1241,8 +1243,9 @@
       <c r="G3" s="4" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="4" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I3" s="15"/>
+    </row>
+    <row r="4" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="6">
         <v>58001</v>
       </c>
@@ -1253,7 +1256,7 @@
         <v>45</v>
       </c>
       <c r="D4" s="2">
-        <v>191</v>
+        <v>177.95</v>
       </c>
       <c r="F4">
         <v>50</v>
@@ -1261,8 +1264,9 @@
       <c r="G4" s="2" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="5" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I4" s="15"/>
+    </row>
+    <row r="5" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="6">
         <v>59502</v>
       </c>
@@ -1273,7 +1277,7 @@
         <v>45</v>
       </c>
       <c r="D5" s="2">
-        <v>216</v>
+        <v>205.06</v>
       </c>
       <c r="F5" s="4">
         <v>0</v>
@@ -1281,8 +1285,9 @@
       <c r="G5" s="2" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="6" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I5" s="15"/>
+    </row>
+    <row r="6" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="6">
         <v>60501</v>
       </c>
@@ -1293,7 +1298,7 @@
         <v>45</v>
       </c>
       <c r="D6" s="2">
-        <v>256</v>
+        <v>238.02</v>
       </c>
       <c r="F6" s="4">
         <v>50</v>
@@ -1301,8 +1306,9 @@
       <c r="G6" s="2" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="7" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I6" s="15"/>
+    </row>
+    <row r="7" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="6">
         <v>56009</v>
       </c>
@@ -1322,7 +1328,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="6">
         <v>57011</v>
       </c>
@@ -1342,7 +1348,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="9" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="6">
         <v>57044</v>
       </c>
@@ -1362,7 +1368,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="10" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="6">
         <v>58014</v>
       </c>
@@ -1382,7 +1388,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="11" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="6">
         <v>59533</v>
       </c>
@@ -1402,7 +1408,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="12" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="9" t="s">
         <v>182</v>
       </c>
@@ -1423,7 +1429,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="13" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>56</v>
       </c>
@@ -1434,7 +1440,7 @@
         <v>78</v>
       </c>
       <c r="D13" s="7">
-        <v>6480.92</v>
+        <v>7020</v>
       </c>
       <c r="F13">
         <v>50</v>
@@ -1443,7 +1449,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="14" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>57</v>
       </c>
@@ -1454,7 +1460,7 @@
         <v>78</v>
       </c>
       <c r="D14" s="7">
-        <v>8841.6200000000008</v>
+        <v>8255</v>
       </c>
       <c r="F14">
         <v>50</v>
@@ -1463,7 +1469,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="15" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>58</v>
       </c>
@@ -1474,10 +1480,7 @@
         <v>78</v>
       </c>
       <c r="D15" s="7">
-        <v>8520.89</v>
-      </c>
-      <c r="E15">
-        <v>5</v>
+        <v>9228.9599999999991</v>
       </c>
       <c r="F15">
         <v>50</v>
@@ -1486,7 +1489,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="16" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>59</v>
       </c>
@@ -1497,7 +1500,7 @@
         <v>78</v>
       </c>
       <c r="D16" s="7">
-        <v>9540.83</v>
+        <v>10335</v>
       </c>
       <c r="F16">
         <v>5</v>

--- a/urunler.xlsx
+++ b/urunler.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\Githup\portal\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78B704A1-28FC-417D-BFE0-BADB106FD471}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{147F9FA0-155B-45AA-9EC0-9E609BB46927}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1216,7 +1216,7 @@
       </c>
       <c r="E2" s="3"/>
       <c r="F2" s="1">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="G2" s="4" t="s">
         <v>46</v>
@@ -1238,7 +1238,7 @@
       </c>
       <c r="E3" s="3"/>
       <c r="F3" s="1">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="G3" s="4" t="s">
         <v>55</v>
@@ -1259,7 +1259,7 @@
         <v>177.95</v>
       </c>
       <c r="F4">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>47</v>
@@ -1280,7 +1280,7 @@
         <v>205.06</v>
       </c>
       <c r="F5" s="4">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>48</v>
@@ -1301,7 +1301,7 @@
         <v>238.02</v>
       </c>
       <c r="F6" s="4">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>49</v>
@@ -1322,7 +1322,7 @@
         <v>81</v>
       </c>
       <c r="F7">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>50</v>
@@ -1342,7 +1342,7 @@
         <v>136</v>
       </c>
       <c r="F8">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>51</v>
@@ -1362,7 +1362,7 @@
         <v>98</v>
       </c>
       <c r="F9">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>52</v>
@@ -1382,7 +1382,7 @@
         <v>116</v>
       </c>
       <c r="F10">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>53</v>
@@ -1402,7 +1402,7 @@
         <v>122</v>
       </c>
       <c r="F11">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>54</v>
@@ -1443,7 +1443,7 @@
         <v>7020</v>
       </c>
       <c r="F13">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>79</v>
@@ -1463,7 +1463,7 @@
         <v>8255</v>
       </c>
       <c r="F14">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="G14" s="2" t="s">
         <v>80</v>
@@ -1483,7 +1483,7 @@
         <v>9228.9599999999991</v>
       </c>
       <c r="F15">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>81</v>

--- a/urunler.xlsx
+++ b/urunler.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\Githup\portal\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{147F9FA0-155B-45AA-9EC0-9E609BB46927}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94924CBA-DFB7-4920-91A5-1A3AB214CE0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="urunler" sheetId="1" r:id="rId1"/>
@@ -2925,7 +2925,7 @@
         <v>29</v>
       </c>
       <c r="C2">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.2">
@@ -2936,7 +2936,7 @@
         <v>30</v>
       </c>
       <c r="C3">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.2">
@@ -2955,7 +2955,7 @@
         <v>188</v>
       </c>
       <c r="C5">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.2">
@@ -2966,7 +2966,7 @@
         <v>189</v>
       </c>
       <c r="C6">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.2">
@@ -2977,7 +2977,7 @@
         <v>190</v>
       </c>
       <c r="C7">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.2">
@@ -3004,7 +3004,7 @@
         <v>193</v>
       </c>
       <c r="C10">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.2">
@@ -3031,7 +3031,7 @@
         <v>265</v>
       </c>
       <c r="C13">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.2">
@@ -3042,7 +3042,7 @@
         <v>266</v>
       </c>
       <c r="C14">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.2">

--- a/urunler.xlsx
+++ b/urunler.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\Githup\portal\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94924CBA-DFB7-4920-91A5-1A3AB214CE0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF462902-6312-43E0-9D4F-89635D1F4985}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="urunler" sheetId="1" r:id="rId1"/>
@@ -923,11 +923,10 @@
     <xf numFmtId="44" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="44" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1182,7 +1181,7 @@
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="C1" s="3" t="s">
         <v>34</v>
       </c>
       <c r="D1" s="1" t="s">
@@ -1197,130 +1196,146 @@
       <c r="G1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="H1" s="3" t="s">
         <v>179</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A2" s="5">
+      <c r="A2" s="4">
         <v>56001</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C2" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="D2" s="12">
+      <c r="D2" s="11">
         <v>140.75</v>
       </c>
-      <c r="E2" s="3"/>
+      <c r="E2">
+        <v>5</v>
+      </c>
       <c r="F2" s="1">
         <v>5</v>
       </c>
-      <c r="G2" s="4" t="s">
+      <c r="G2" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="I2" s="15"/>
+      <c r="I2" s="14"/>
     </row>
     <row r="3" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A3" s="5">
+      <c r="A3" s="4">
         <v>57001</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="D3" s="12">
+      <c r="D3" s="11">
         <v>162.76</v>
       </c>
-      <c r="E3" s="3"/>
+      <c r="E3">
+        <v>5</v>
+      </c>
       <c r="F3" s="1">
         <v>5</v>
       </c>
-      <c r="G3" s="4" t="s">
+      <c r="G3" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="I3" s="15"/>
+      <c r="I3" s="14"/>
     </row>
     <row r="4" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="6">
+      <c r="A4" s="5">
         <v>58001</v>
       </c>
       <c r="B4" t="s">
         <v>37</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="C4" s="3" t="s">
         <v>45</v>
       </c>
       <c r="D4" s="2">
         <v>177.95</v>
       </c>
+      <c r="E4">
+        <v>5</v>
+      </c>
       <c r="F4">
         <v>5</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="I4" s="15"/>
+      <c r="I4" s="14"/>
     </row>
     <row r="5" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="6">
+      <c r="A5" s="5">
         <v>59502</v>
       </c>
       <c r="B5" t="s">
         <v>38</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="C5" s="3" t="s">
         <v>45</v>
       </c>
       <c r="D5" s="2">
         <v>205.06</v>
       </c>
-      <c r="F5" s="4">
+      <c r="E5">
+        <v>5</v>
+      </c>
+      <c r="F5" s="3">
         <v>25</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="I5" s="15"/>
+      <c r="I5" s="14"/>
     </row>
     <row r="6" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="6">
+      <c r="A6" s="5">
         <v>60501</v>
       </c>
       <c r="B6" t="s">
         <v>39</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="C6" s="3" t="s">
         <v>45</v>
       </c>
       <c r="D6" s="2">
         <v>238.02</v>
       </c>
-      <c r="F6" s="4">
+      <c r="E6">
+        <v>5</v>
+      </c>
+      <c r="F6" s="3">
         <v>5</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="I6" s="15"/>
+      <c r="I6" s="14"/>
     </row>
     <row r="7" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="6">
+      <c r="A7" s="5">
         <v>56009</v>
       </c>
       <c r="B7" t="s">
         <v>40</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="C7" s="3" t="s">
         <v>45</v>
       </c>
       <c r="D7" s="2">
         <v>81</v>
       </c>
+      <c r="E7">
+        <v>5</v>
+      </c>
       <c r="F7">
         <v>5</v>
       </c>
@@ -1329,18 +1344,21 @@
       </c>
     </row>
     <row r="8" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="6">
+      <c r="A8" s="5">
         <v>57011</v>
       </c>
       <c r="B8" t="s">
         <v>41</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="C8" s="3" t="s">
         <v>45</v>
       </c>
       <c r="D8" s="2">
         <v>136</v>
       </c>
+      <c r="E8">
+        <v>5</v>
+      </c>
       <c r="F8">
         <v>5</v>
       </c>
@@ -1349,18 +1367,21 @@
       </c>
     </row>
     <row r="9" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="6">
+      <c r="A9" s="5">
         <v>57044</v>
       </c>
       <c r="B9" t="s">
         <v>42</v>
       </c>
-      <c r="C9" s="4" t="s">
+      <c r="C9" s="3" t="s">
         <v>45</v>
       </c>
       <c r="D9" s="2">
         <v>98</v>
       </c>
+      <c r="E9">
+        <v>5</v>
+      </c>
       <c r="F9">
         <v>5</v>
       </c>
@@ -1369,18 +1390,21 @@
       </c>
     </row>
     <row r="10" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="6">
+      <c r="A10" s="5">
         <v>58014</v>
       </c>
       <c r="B10" t="s">
         <v>43</v>
       </c>
-      <c r="C10" s="4" t="s">
+      <c r="C10" s="3" t="s">
         <v>45</v>
       </c>
       <c r="D10" s="2">
         <v>116</v>
       </c>
+      <c r="E10">
+        <v>5</v>
+      </c>
       <c r="F10">
         <v>5</v>
       </c>
@@ -1389,18 +1413,21 @@
       </c>
     </row>
     <row r="11" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="6">
+      <c r="A11" s="5">
         <v>59533</v>
       </c>
       <c r="B11" t="s">
         <v>44</v>
       </c>
-      <c r="C11" s="4" t="s">
+      <c r="C11" s="3" t="s">
         <v>45</v>
       </c>
       <c r="D11" s="2">
         <v>122</v>
       </c>
+      <c r="E11">
+        <v>5</v>
+      </c>
       <c r="F11">
         <v>5</v>
       </c>
@@ -1409,23 +1436,25 @@
       </c>
     </row>
     <row r="12" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="9" t="s">
+      <c r="A12" s="8" t="s">
         <v>182</v>
       </c>
-      <c r="B12" s="10" t="s">
+      <c r="B12" s="9" t="s">
         <v>183</v>
       </c>
-      <c r="C12" s="10" t="s">
+      <c r="C12" s="9" t="s">
         <v>45</v>
       </c>
-      <c r="D12" s="7">
+      <c r="D12" s="6">
         <v>48.77</v>
       </c>
-      <c r="E12" s="2"/>
+      <c r="E12">
+        <v>5</v>
+      </c>
       <c r="F12" s="2">
         <v>2</v>
       </c>
-      <c r="G12" s="11" t="s">
+      <c r="G12" s="10" t="s">
         <v>184</v>
       </c>
     </row>
@@ -1439,8 +1468,11 @@
       <c r="C13" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="D13" s="7">
+      <c r="D13" s="6">
         <v>7020</v>
+      </c>
+      <c r="E13">
+        <v>10</v>
       </c>
       <c r="F13">
         <v>5</v>
@@ -1459,8 +1491,11 @@
       <c r="C14" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="D14" s="7">
+      <c r="D14" s="6">
         <v>8255</v>
+      </c>
+      <c r="E14">
+        <v>10</v>
       </c>
       <c r="F14">
         <v>5</v>
@@ -1479,8 +1514,11 @@
       <c r="C15" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="D15" s="7">
+      <c r="D15" s="6">
         <v>9228.9599999999991</v>
+      </c>
+      <c r="E15">
+        <v>10</v>
       </c>
       <c r="F15">
         <v>5</v>
@@ -1499,8 +1537,11 @@
       <c r="C16" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="D16" s="7">
+      <c r="D16" s="6">
         <v>10335</v>
+      </c>
+      <c r="E16">
+        <v>10</v>
       </c>
       <c r="F16">
         <v>5</v>
@@ -1519,8 +1560,11 @@
       <c r="C17" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="D17" s="7">
+      <c r="D17" s="6">
         <v>7620.91</v>
+      </c>
+      <c r="E17">
+        <v>10</v>
       </c>
       <c r="F17">
         <v>5</v>
@@ -1539,8 +1583,11 @@
       <c r="C18" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="D18" s="7">
+      <c r="D18" s="6">
         <v>2577.54</v>
+      </c>
+      <c r="E18">
+        <v>10</v>
       </c>
       <c r="F18">
         <v>5</v>
@@ -1559,8 +1606,11 @@
       <c r="C19" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="D19" s="7">
+      <c r="D19" s="6">
         <v>2550.75</v>
+      </c>
+      <c r="E19">
+        <v>10</v>
       </c>
       <c r="F19">
         <v>5</v>
@@ -1579,8 +1629,11 @@
       <c r="C20" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="D20" s="7">
+      <c r="D20" s="6">
         <v>3226.53</v>
+      </c>
+      <c r="E20">
+        <v>10</v>
       </c>
       <c r="F20">
         <v>5</v>
@@ -1599,8 +1652,11 @@
       <c r="C21" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="D21" s="7">
+      <c r="D21" s="6">
         <v>3611.43</v>
+      </c>
+      <c r="E21">
+        <v>10</v>
       </c>
       <c r="F21">
         <v>5</v>
@@ -1619,8 +1675,11 @@
       <c r="C22" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="D22" s="7">
+      <c r="D22" s="6">
         <v>3828.73</v>
+      </c>
+      <c r="E22">
+        <v>10</v>
       </c>
       <c r="F22">
         <v>5</v>
@@ -1639,8 +1698,11 @@
       <c r="C23" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="D23" s="7">
+      <c r="D23" s="6">
         <v>4020.83</v>
+      </c>
+      <c r="E23">
+        <v>10</v>
       </c>
       <c r="F23">
         <v>5</v>
@@ -1659,8 +1721,11 @@
       <c r="C24" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="D24" s="7">
+      <c r="D24" s="6">
         <v>4020.91</v>
+      </c>
+      <c r="E24">
+        <v>10</v>
       </c>
       <c r="F24">
         <v>5</v>
@@ -1670,7 +1735,7 @@
       </c>
     </row>
     <row r="25" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="6">
+      <c r="A25" s="5">
         <v>10089</v>
       </c>
       <c r="B25" t="s">
@@ -1679,8 +1744,11 @@
       <c r="C25" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="D25" s="7">
+      <c r="D25" s="6">
         <v>4386.92</v>
+      </c>
+      <c r="E25">
+        <v>10</v>
       </c>
       <c r="F25">
         <v>5</v>
@@ -1702,6 +1770,9 @@
       <c r="D26">
         <v>728.72</v>
       </c>
+      <c r="E26">
+        <v>5</v>
+      </c>
       <c r="F26">
         <v>5</v>
       </c>
@@ -1725,6 +1796,9 @@
       <c r="D27">
         <v>474.36</v>
       </c>
+      <c r="E27">
+        <v>5</v>
+      </c>
       <c r="F27">
         <v>5</v>
       </c>
@@ -1748,6 +1822,9 @@
       <c r="D28">
         <v>522.48</v>
       </c>
+      <c r="E28">
+        <v>5</v>
+      </c>
       <c r="F28">
         <v>5</v>
       </c>
@@ -1771,6 +1848,9 @@
       <c r="D29">
         <v>653.98</v>
       </c>
+      <c r="E29">
+        <v>5</v>
+      </c>
       <c r="F29">
         <v>5</v>
       </c>
@@ -1782,10 +1862,10 @@
       </c>
     </row>
     <row r="30" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="8" t="s">
+      <c r="A30" s="7" t="s">
         <v>102</v>
       </c>
-      <c r="B30" s="8" t="s">
+      <c r="B30" s="7" t="s">
         <v>126</v>
       </c>
       <c r="C30" s="2" t="s">
@@ -1794,6 +1874,9 @@
       <c r="D30">
         <v>172.59</v>
       </c>
+      <c r="E30">
+        <v>5</v>
+      </c>
       <c r="F30">
         <v>24</v>
       </c>
@@ -1805,10 +1888,10 @@
       </c>
     </row>
     <row r="31" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="8" t="s">
+      <c r="A31" s="7" t="s">
         <v>103</v>
       </c>
-      <c r="B31" s="8" t="s">
+      <c r="B31" s="7" t="s">
         <v>127</v>
       </c>
       <c r="C31" s="2" t="s">
@@ -1817,6 +1900,9 @@
       <c r="D31">
         <v>172.59</v>
       </c>
+      <c r="E31">
+        <v>5</v>
+      </c>
       <c r="G31" s="2" t="s">
         <v>130</v>
       </c>
@@ -1825,10 +1911,10 @@
       </c>
     </row>
     <row r="32" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="8" t="s">
+      <c r="A32" s="7" t="s">
         <v>104</v>
       </c>
-      <c r="B32" s="8" t="s">
+      <c r="B32" s="7" t="s">
         <v>171</v>
       </c>
       <c r="C32" s="2" t="s">
@@ -1837,6 +1923,9 @@
       <c r="D32">
         <v>21.69</v>
       </c>
+      <c r="E32">
+        <v>5</v>
+      </c>
       <c r="F32">
         <v>108</v>
       </c>
@@ -1848,10 +1937,10 @@
       </c>
     </row>
     <row r="33" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="8" t="s">
+      <c r="A33" s="7" t="s">
         <v>105</v>
       </c>
-      <c r="B33" s="8" t="s">
+      <c r="B33" s="7" t="s">
         <v>159</v>
       </c>
       <c r="C33" s="2" t="s">
@@ -1860,6 +1949,9 @@
       <c r="D33">
         <v>198.99</v>
       </c>
+      <c r="E33">
+        <v>5</v>
+      </c>
       <c r="F33">
         <v>80</v>
       </c>
@@ -1871,10 +1963,10 @@
       </c>
     </row>
     <row r="34" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="8" t="s">
+      <c r="A34" s="7" t="s">
         <v>106</v>
       </c>
-      <c r="B34" s="8" t="s">
+      <c r="B34" s="7" t="s">
         <v>160</v>
       </c>
       <c r="C34" s="2" t="s">
@@ -1883,6 +1975,9 @@
       <c r="D34">
         <v>144.99</v>
       </c>
+      <c r="E34">
+        <v>5</v>
+      </c>
       <c r="F34">
         <v>216</v>
       </c>
@@ -1894,10 +1989,10 @@
       </c>
     </row>
     <row r="35" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="8" t="s">
+      <c r="A35" s="7" t="s">
         <v>107</v>
       </c>
-      <c r="B35" s="8" t="s">
+      <c r="B35" s="7" t="s">
         <v>161</v>
       </c>
       <c r="C35" s="2" t="s">
@@ -1906,6 +2001,9 @@
       <c r="D35">
         <v>165</v>
       </c>
+      <c r="E35">
+        <v>5</v>
+      </c>
       <c r="F35">
         <v>69</v>
       </c>
@@ -1917,10 +2015,10 @@
       </c>
     </row>
     <row r="36" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="8" t="s">
+      <c r="A36" s="7" t="s">
         <v>108</v>
       </c>
-      <c r="B36" s="8" t="s">
+      <c r="B36" s="7" t="s">
         <v>162</v>
       </c>
       <c r="C36" s="2" t="s">
@@ -1929,6 +2027,9 @@
       <c r="D36">
         <v>179.4</v>
       </c>
+      <c r="E36">
+        <v>5</v>
+      </c>
       <c r="F36">
         <v>61</v>
       </c>
@@ -1940,10 +2041,10 @@
       </c>
     </row>
     <row r="37" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="8" t="s">
+      <c r="A37" s="7" t="s">
         <v>109</v>
       </c>
-      <c r="B37" s="8" t="s">
+      <c r="B37" s="7" t="s">
         <v>163</v>
       </c>
       <c r="C37" s="2" t="s">
@@ -1952,6 +2053,9 @@
       <c r="D37">
         <v>300</v>
       </c>
+      <c r="E37">
+        <v>5</v>
+      </c>
       <c r="F37">
         <v>76</v>
       </c>
@@ -1963,10 +2067,10 @@
       </c>
     </row>
     <row r="38" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="8" t="s">
+      <c r="A38" s="7" t="s">
         <v>110</v>
       </c>
-      <c r="B38" s="8" t="s">
+      <c r="B38" s="7" t="s">
         <v>164</v>
       </c>
       <c r="C38" s="2" t="s">
@@ -1975,6 +2079,9 @@
       <c r="D38">
         <v>225</v>
       </c>
+      <c r="E38">
+        <v>5</v>
+      </c>
       <c r="F38">
         <v>47</v>
       </c>
@@ -1986,10 +2093,10 @@
       </c>
     </row>
     <row r="39" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="8" t="s">
+      <c r="A39" s="7" t="s">
         <v>111</v>
       </c>
-      <c r="B39" s="8" t="s">
+      <c r="B39" s="7" t="s">
         <v>165</v>
       </c>
       <c r="C39" s="2" t="s">
@@ -1998,6 +2105,9 @@
       <c r="D39">
         <v>150</v>
       </c>
+      <c r="E39">
+        <v>5</v>
+      </c>
       <c r="F39">
         <v>16</v>
       </c>
@@ -2009,10 +2119,10 @@
       </c>
     </row>
     <row r="40" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="8" t="s">
+      <c r="A40" s="7" t="s">
         <v>112</v>
       </c>
-      <c r="B40" s="8" t="s">
+      <c r="B40" s="7" t="s">
         <v>166</v>
       </c>
       <c r="C40" s="2" t="s">
@@ -2021,6 +2131,9 @@
       <c r="D40">
         <v>300</v>
       </c>
+      <c r="E40">
+        <v>5</v>
+      </c>
       <c r="F40">
         <v>21</v>
       </c>
@@ -2032,10 +2145,10 @@
       </c>
     </row>
     <row r="41" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="8" t="s">
+      <c r="A41" s="7" t="s">
         <v>113</v>
       </c>
-      <c r="B41" s="8" t="s">
+      <c r="B41" s="7" t="s">
         <v>167</v>
       </c>
       <c r="C41" s="2" t="s">
@@ -2044,6 +2157,9 @@
       <c r="D41">
         <v>52.8</v>
       </c>
+      <c r="E41">
+        <v>5</v>
+      </c>
       <c r="F41">
         <v>96</v>
       </c>
@@ -2055,10 +2171,10 @@
       </c>
     </row>
     <row r="42" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="8" t="s">
+      <c r="A42" s="7" t="s">
         <v>114</v>
       </c>
-      <c r="B42" s="8" t="s">
+      <c r="B42" s="7" t="s">
         <v>168</v>
       </c>
       <c r="C42" s="2" t="s">
@@ -2067,6 +2183,9 @@
       <c r="D42">
         <v>255</v>
       </c>
+      <c r="E42">
+        <v>5</v>
+      </c>
       <c r="F42">
         <v>58</v>
       </c>
@@ -2078,10 +2197,10 @@
       </c>
     </row>
     <row r="43" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A43" s="8" t="s">
+      <c r="A43" s="7" t="s">
         <v>115</v>
       </c>
-      <c r="B43" s="8" t="s">
+      <c r="B43" s="7" t="s">
         <v>169</v>
       </c>
       <c r="C43" s="2" t="s">
@@ -2090,6 +2209,9 @@
       <c r="D43">
         <v>128.4</v>
       </c>
+      <c r="E43">
+        <v>5</v>
+      </c>
       <c r="F43">
         <v>12</v>
       </c>
@@ -2101,10 +2223,10 @@
       </c>
     </row>
     <row r="44" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A44" s="8" t="s">
+      <c r="A44" s="7" t="s">
         <v>116</v>
       </c>
-      <c r="B44" s="8" t="s">
+      <c r="B44" s="7" t="s">
         <v>170</v>
       </c>
       <c r="C44" s="2" t="s">
@@ -2113,6 +2235,9 @@
       <c r="D44">
         <v>127.19999999999999</v>
       </c>
+      <c r="E44">
+        <v>5</v>
+      </c>
       <c r="F44">
         <v>24</v>
       </c>
@@ -2124,10 +2249,10 @@
       </c>
     </row>
     <row r="45" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A45" s="8" t="s">
+      <c r="A45" s="7" t="s">
         <v>117</v>
       </c>
-      <c r="B45" s="8" t="s">
+      <c r="B45" s="7" t="s">
         <v>128</v>
       </c>
       <c r="C45" s="2" t="s">
@@ -2136,6 +2261,9 @@
       <c r="D45">
         <v>180</v>
       </c>
+      <c r="E45">
+        <v>5</v>
+      </c>
       <c r="F45">
         <v>67</v>
       </c>
@@ -2147,10 +2275,10 @@
       </c>
     </row>
     <row r="46" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A46" s="8" t="s">
+      <c r="A46" s="7" t="s">
         <v>118</v>
       </c>
-      <c r="B46" s="8" t="s">
+      <c r="B46" s="7" t="s">
         <v>172</v>
       </c>
       <c r="C46" s="2" t="s">
@@ -2159,6 +2287,9 @@
       <c r="D46">
         <v>202.79999999999998</v>
       </c>
+      <c r="E46">
+        <v>5</v>
+      </c>
       <c r="F46">
         <v>254</v>
       </c>
@@ -2170,10 +2301,10 @@
       </c>
     </row>
     <row r="47" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A47" s="8" t="s">
+      <c r="A47" s="7" t="s">
         <v>119</v>
       </c>
-      <c r="B47" s="8" t="s">
+      <c r="B47" s="7" t="s">
         <v>174</v>
       </c>
       <c r="C47" s="2" t="s">
@@ -2182,6 +2313,9 @@
       <c r="D47">
         <v>127.19999999999999</v>
       </c>
+      <c r="E47">
+        <v>5</v>
+      </c>
       <c r="F47">
         <v>5</v>
       </c>
@@ -2193,10 +2327,10 @@
       </c>
     </row>
     <row r="48" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A48" s="8" t="s">
+      <c r="A48" s="7" t="s">
         <v>120</v>
       </c>
-      <c r="B48" s="8" t="s">
+      <c r="B48" s="7" t="s">
         <v>173</v>
       </c>
       <c r="C48" s="2" t="s">
@@ -2205,6 +2339,9 @@
       <c r="D48">
         <v>150</v>
       </c>
+      <c r="E48">
+        <v>5</v>
+      </c>
       <c r="G48" s="2" t="s">
         <v>147</v>
       </c>
@@ -2213,10 +2350,10 @@
       </c>
     </row>
     <row r="49" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A49" s="8" t="s">
+      <c r="A49" s="7" t="s">
         <v>121</v>
       </c>
-      <c r="B49" s="8" t="s">
+      <c r="B49" s="7" t="s">
         <v>175</v>
       </c>
       <c r="C49" s="2" t="s">
@@ -2225,6 +2362,9 @@
       <c r="D49">
         <v>156</v>
       </c>
+      <c r="E49">
+        <v>5</v>
+      </c>
       <c r="F49">
         <v>46</v>
       </c>
@@ -2236,10 +2376,10 @@
       </c>
     </row>
     <row r="50" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A50" s="8" t="s">
+      <c r="A50" s="7" t="s">
         <v>122</v>
       </c>
-      <c r="B50" s="8" t="s">
+      <c r="B50" s="7" t="s">
         <v>176</v>
       </c>
       <c r="C50" s="2" t="s">
@@ -2248,6 +2388,9 @@
       <c r="D50">
         <v>144</v>
       </c>
+      <c r="E50">
+        <v>5</v>
+      </c>
       <c r="G50" s="2" t="s">
         <v>149</v>
       </c>
@@ -2256,10 +2399,10 @@
       </c>
     </row>
     <row r="51" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A51" s="8" t="s">
+      <c r="A51" s="7" t="s">
         <v>123</v>
       </c>
-      <c r="B51" s="8" t="s">
+      <c r="B51" s="7" t="s">
         <v>177</v>
       </c>
       <c r="C51" s="2" t="s">
@@ -2268,6 +2411,9 @@
       <c r="D51">
         <v>194.4</v>
       </c>
+      <c r="E51">
+        <v>5</v>
+      </c>
       <c r="F51">
         <v>120</v>
       </c>
@@ -2279,10 +2425,10 @@
       </c>
     </row>
     <row r="52" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A52" s="8" t="s">
+      <c r="A52" s="7" t="s">
         <v>124</v>
       </c>
-      <c r="B52" s="8" t="s">
+      <c r="B52" s="7" t="s">
         <v>178</v>
       </c>
       <c r="C52" s="2" t="s">
@@ -2291,6 +2437,9 @@
       <c r="D52">
         <v>285</v>
       </c>
+      <c r="E52">
+        <v>5</v>
+      </c>
       <c r="F52">
         <v>39</v>
       </c>
@@ -2302,23 +2451,23 @@
       </c>
     </row>
     <row r="53" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A53" s="9" t="s">
+      <c r="A53" s="8" t="s">
         <v>180</v>
       </c>
-      <c r="B53" s="10" t="s">
+      <c r="B53" s="9" t="s">
         <v>185</v>
       </c>
-      <c r="C53" s="10" t="s">
+      <c r="C53" s="9" t="s">
         <v>125</v>
       </c>
-      <c r="D53" s="11">
+      <c r="D53" s="10">
         <v>60</v>
       </c>
       <c r="E53" s="2"/>
       <c r="F53" s="2">
         <v>120</v>
       </c>
-      <c r="G53" s="11" t="s">
+      <c r="G53" s="10" t="s">
         <v>181</v>
       </c>
       <c r="H53">
@@ -2326,10 +2475,10 @@
       </c>
     </row>
     <row r="54" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A54" s="8" t="s">
+      <c r="A54" s="7" t="s">
         <v>152</v>
       </c>
-      <c r="B54" s="8" t="s">
+      <c r="B54" s="7" t="s">
         <v>153</v>
       </c>
       <c r="G54" s="2" t="s">
@@ -2337,10 +2486,10 @@
       </c>
     </row>
     <row r="55" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A55" s="8" t="s">
+      <c r="A55" s="7" t="s">
         <v>152</v>
       </c>
-      <c r="B55" s="8" t="s">
+      <c r="B55" s="7" t="s">
         <v>154</v>
       </c>
       <c r="G55" s="2" t="s">
@@ -2348,10 +2497,10 @@
       </c>
     </row>
     <row r="56" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A56" s="8" t="s">
+      <c r="A56" s="7" t="s">
         <v>152</v>
       </c>
-      <c r="B56" s="8" t="s">
+      <c r="B56" s="7" t="s">
         <v>157</v>
       </c>
       <c r="G56" s="2" t="s">
@@ -2359,10 +2508,10 @@
       </c>
     </row>
     <row r="57" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A57" s="8" t="s">
+      <c r="A57" s="7" t="s">
         <v>152</v>
       </c>
-      <c r="B57" s="8" t="s">
+      <c r="B57" s="7" t="s">
         <v>221</v>
       </c>
       <c r="G57" s="2" t="s">
@@ -2370,10 +2519,10 @@
       </c>
     </row>
     <row r="58" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A58" s="8" t="s">
+      <c r="A58" s="7" t="s">
         <v>152</v>
       </c>
-      <c r="B58" s="8" t="s">
+      <c r="B58" s="7" t="s">
         <v>222</v>
       </c>
       <c r="G58" s="2" t="s">
@@ -2381,19 +2530,19 @@
       </c>
     </row>
     <row r="59" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A59" s="14" t="s">
+      <c r="A59" s="13" t="s">
         <v>196</v>
       </c>
-      <c r="B59" s="14" t="s">
+      <c r="B59" s="13" t="s">
         <v>197</v>
       </c>
-      <c r="C59" s="14" t="s">
+      <c r="C59" s="13" t="s">
         <v>212</v>
       </c>
-      <c r="D59" s="13">
+      <c r="D59" s="12">
         <v>5583.15</v>
       </c>
-      <c r="E59" s="13"/>
+      <c r="E59" s="12"/>
       <c r="F59">
         <v>5</v>
       </c>
@@ -2402,19 +2551,19 @@
       </c>
     </row>
     <row r="60" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A60" s="14" t="s">
+      <c r="A60" s="13" t="s">
         <v>198</v>
       </c>
-      <c r="B60" s="14" t="s">
+      <c r="B60" s="13" t="s">
         <v>199</v>
       </c>
-      <c r="C60" s="14" t="s">
+      <c r="C60" s="13" t="s">
         <v>212</v>
       </c>
-      <c r="D60" s="13">
+      <c r="D60" s="12">
         <v>883.37</v>
       </c>
-      <c r="E60" s="13"/>
+      <c r="E60" s="12"/>
       <c r="F60">
         <v>5</v>
       </c>
@@ -2423,19 +2572,19 @@
       </c>
     </row>
     <row r="61" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A61" s="14" t="s">
+      <c r="A61" s="13" t="s">
         <v>200</v>
       </c>
-      <c r="B61" s="14" t="s">
+      <c r="B61" s="13" t="s">
         <v>201</v>
       </c>
-      <c r="C61" s="14" t="s">
+      <c r="C61" s="13" t="s">
         <v>212</v>
       </c>
-      <c r="D61" s="13">
+      <c r="D61" s="12">
         <v>2658.06</v>
       </c>
-      <c r="E61" s="13"/>
+      <c r="E61" s="12"/>
       <c r="F61">
         <v>5</v>
       </c>
@@ -2444,19 +2593,19 @@
       </c>
     </row>
     <row r="62" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A62" s="14" t="s">
+      <c r="A62" s="13" t="s">
         <v>202</v>
       </c>
-      <c r="B62" s="14" t="s">
+      <c r="B62" s="13" t="s">
         <v>203</v>
       </c>
-      <c r="C62" s="14" t="s">
+      <c r="C62" s="13" t="s">
         <v>212</v>
       </c>
-      <c r="D62" s="13">
+      <c r="D62" s="12">
         <v>2519.23</v>
       </c>
-      <c r="E62" s="13"/>
+      <c r="E62" s="12"/>
       <c r="F62">
         <v>5</v>
       </c>
@@ -2465,19 +2614,19 @@
       </c>
     </row>
     <row r="63" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A63" s="14" t="s">
+      <c r="A63" s="13" t="s">
         <v>204</v>
       </c>
-      <c r="B63" s="14" t="s">
+      <c r="B63" s="13" t="s">
         <v>205</v>
       </c>
-      <c r="C63" s="14" t="s">
+      <c r="C63" s="13" t="s">
         <v>212</v>
       </c>
-      <c r="D63" s="13">
+      <c r="D63" s="12">
         <v>1838.36</v>
       </c>
-      <c r="E63" s="13"/>
+      <c r="E63" s="12"/>
       <c r="F63">
         <v>5</v>
       </c>
@@ -2486,19 +2635,19 @@
       </c>
     </row>
     <row r="64" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A64" s="14" t="s">
+      <c r="A64" s="13" t="s">
         <v>206</v>
       </c>
-      <c r="B64" s="14" t="s">
+      <c r="B64" s="13" t="s">
         <v>207</v>
       </c>
-      <c r="C64" s="14" t="s">
+      <c r="C64" s="13" t="s">
         <v>212</v>
       </c>
-      <c r="D64" s="13">
+      <c r="D64" s="12">
         <v>1153.95</v>
       </c>
-      <c r="E64" s="13"/>
+      <c r="E64" s="12"/>
       <c r="F64">
         <v>5</v>
       </c>
@@ -2507,19 +2656,19 @@
       </c>
     </row>
     <row r="65" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A65" s="14" t="s">
+      <c r="A65" s="13" t="s">
         <v>208</v>
       </c>
-      <c r="B65" s="14" t="s">
+      <c r="B65" s="13" t="s">
         <v>209</v>
       </c>
-      <c r="C65" s="14" t="s">
+      <c r="C65" s="13" t="s">
         <v>212</v>
       </c>
-      <c r="D65" s="13">
+      <c r="D65" s="12">
         <v>5583.15</v>
       </c>
-      <c r="E65" s="13"/>
+      <c r="E65" s="12"/>
       <c r="F65">
         <v>5</v>
       </c>
@@ -2528,19 +2677,19 @@
       </c>
     </row>
     <row r="66" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A66" s="14" t="s">
+      <c r="A66" s="13" t="s">
         <v>210</v>
       </c>
-      <c r="B66" s="14" t="s">
+      <c r="B66" s="13" t="s">
         <v>211</v>
       </c>
-      <c r="C66" s="14" t="s">
+      <c r="C66" s="13" t="s">
         <v>212</v>
       </c>
-      <c r="D66" s="13">
+      <c r="D66" s="12">
         <v>596.87</v>
       </c>
-      <c r="E66" s="13"/>
+      <c r="E66" s="12"/>
       <c r="F66">
         <v>5</v>
       </c>
@@ -2549,13 +2698,13 @@
       </c>
     </row>
     <row r="67" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A67" s="6">
+      <c r="A67" s="5">
         <v>8899142</v>
       </c>
       <c r="B67" t="s">
         <v>225</v>
       </c>
-      <c r="C67" s="14" t="s">
+      <c r="C67" s="13" t="s">
         <v>78</v>
       </c>
       <c r="D67">
@@ -2572,13 +2721,13 @@
       </c>
     </row>
     <row r="68" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A68" s="6">
+      <c r="A68" s="5">
         <v>8899143</v>
       </c>
       <c r="B68" t="s">
         <v>226</v>
       </c>
-      <c r="C68" s="14" t="s">
+      <c r="C68" s="13" t="s">
         <v>78</v>
       </c>
       <c r="D68">
@@ -2595,13 +2744,13 @@
       </c>
     </row>
     <row r="69" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A69" s="6">
+      <c r="A69" s="5">
         <v>8899145</v>
       </c>
       <c r="B69" t="s">
         <v>227</v>
       </c>
-      <c r="C69" s="14" t="s">
+      <c r="C69" s="13" t="s">
         <v>78</v>
       </c>
       <c r="D69">
@@ -2618,13 +2767,13 @@
       </c>
     </row>
     <row r="70" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A70" s="6">
+      <c r="A70" s="5">
         <v>8899146</v>
       </c>
       <c r="B70" t="s">
         <v>228</v>
       </c>
-      <c r="C70" s="14" t="s">
+      <c r="C70" s="13" t="s">
         <v>78</v>
       </c>
       <c r="D70">
@@ -2647,7 +2796,7 @@
       <c r="B71" t="s">
         <v>229</v>
       </c>
-      <c r="C71" s="14" t="s">
+      <c r="C71" s="13" t="s">
         <v>78</v>
       </c>
       <c r="D71">
@@ -2670,7 +2819,7 @@
       <c r="B72" t="s">
         <v>230</v>
       </c>
-      <c r="C72" s="14" t="s">
+      <c r="C72" s="13" t="s">
         <v>78</v>
       </c>
       <c r="D72">
@@ -2693,7 +2842,7 @@
       <c r="B73" t="s">
         <v>231</v>
       </c>
-      <c r="C73" s="14" t="s">
+      <c r="C73" s="13" t="s">
         <v>78</v>
       </c>
       <c r="D73">
@@ -2716,7 +2865,7 @@
       <c r="B74" t="s">
         <v>232</v>
       </c>
-      <c r="C74" s="14" t="s">
+      <c r="C74" s="13" t="s">
         <v>78</v>
       </c>
       <c r="D74">
@@ -2739,7 +2888,7 @@
       <c r="B75" t="s">
         <v>237</v>
       </c>
-      <c r="C75" s="14" t="s">
+      <c r="C75" s="13" t="s">
         <v>78</v>
       </c>
       <c r="D75">
@@ -2756,13 +2905,13 @@
       </c>
     </row>
     <row r="76" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A76" s="8" t="s">
+      <c r="A76" s="7" t="s">
         <v>257</v>
       </c>
-      <c r="B76" s="8" t="s">
+      <c r="B76" s="7" t="s">
         <v>248</v>
       </c>
-      <c r="C76" s="14" t="s">
+      <c r="C76" s="13" t="s">
         <v>256</v>
       </c>
       <c r="D76">
@@ -2773,13 +2922,13 @@
       </c>
     </row>
     <row r="77" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A77" s="8" t="s">
+      <c r="A77" s="7" t="s">
         <v>258</v>
       </c>
-      <c r="B77" s="8" t="s">
+      <c r="B77" s="7" t="s">
         <v>249</v>
       </c>
-      <c r="C77" s="14" t="s">
+      <c r="C77" s="13" t="s">
         <v>256</v>
       </c>
       <c r="D77">
@@ -2790,13 +2939,13 @@
       </c>
     </row>
     <row r="78" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A78" s="8" t="s">
+      <c r="A78" s="7" t="s">
         <v>259</v>
       </c>
-      <c r="B78" s="8" t="s">
+      <c r="B78" s="7" t="s">
         <v>250</v>
       </c>
-      <c r="C78" s="14" t="s">
+      <c r="C78" s="13" t="s">
         <v>256</v>
       </c>
       <c r="D78">
@@ -2807,13 +2956,13 @@
       </c>
     </row>
     <row r="79" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A79" s="8" t="s">
+      <c r="A79" s="7" t="s">
         <v>260</v>
       </c>
-      <c r="B79" s="8" t="s">
+      <c r="B79" s="7" t="s">
         <v>251</v>
       </c>
-      <c r="C79" s="14" t="s">
+      <c r="C79" s="13" t="s">
         <v>256</v>
       </c>
       <c r="D79">
@@ -2824,13 +2973,13 @@
       </c>
     </row>
     <row r="80" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A80" s="8" t="s">
+      <c r="A80" s="7" t="s">
         <v>261</v>
       </c>
-      <c r="B80" s="8" t="s">
+      <c r="B80" s="7" t="s">
         <v>252</v>
       </c>
-      <c r="C80" s="14" t="s">
+      <c r="C80" s="13" t="s">
         <v>256</v>
       </c>
       <c r="D80">
@@ -2841,13 +2990,13 @@
       </c>
     </row>
     <row r="81" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A81" s="8" t="s">
+      <c r="A81" s="7" t="s">
         <v>262</v>
       </c>
-      <c r="B81" s="8" t="s">
+      <c r="B81" s="7" t="s">
         <v>253</v>
       </c>
-      <c r="C81" s="14" t="s">
+      <c r="C81" s="13" t="s">
         <v>256</v>
       </c>
       <c r="D81">
@@ -2858,13 +3007,13 @@
       </c>
     </row>
     <row r="82" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A82" s="8" t="s">
+      <c r="A82" s="7" t="s">
         <v>263</v>
       </c>
-      <c r="B82" s="8" t="s">
+      <c r="B82" s="7" t="s">
         <v>254</v>
       </c>
-      <c r="C82" s="14" t="s">
+      <c r="C82" s="13" t="s">
         <v>256</v>
       </c>
       <c r="D82">
@@ -2875,13 +3024,13 @@
       </c>
     </row>
     <row r="83" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A83" s="8" t="s">
+      <c r="A83" s="7" t="s">
         <v>264</v>
       </c>
-      <c r="B83" s="8" t="s">
+      <c r="B83" s="7" t="s">
         <v>255</v>
       </c>
-      <c r="C83" s="14" t="s">
+      <c r="C83" s="13" t="s">
         <v>256</v>
       </c>
       <c r="D83">
@@ -2924,9 +3073,6 @@
       <c r="B2" t="s">
         <v>29</v>
       </c>
-      <c r="C2">
-        <v>5</v>
-      </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
@@ -2935,9 +3081,6 @@
       <c r="B3" t="s">
         <v>30</v>
       </c>
-      <c r="C3">
-        <v>5</v>
-      </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
@@ -2954,9 +3097,6 @@
       <c r="B5" s="2" t="s">
         <v>188</v>
       </c>
-      <c r="C5">
-        <v>5</v>
-      </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
@@ -2965,9 +3105,6 @@
       <c r="B6" s="2" t="s">
         <v>189</v>
       </c>
-      <c r="C6">
-        <v>5</v>
-      </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
@@ -2976,9 +3113,6 @@
       <c r="B7" s="2" t="s">
         <v>190</v>
       </c>
-      <c r="C7">
-        <v>5</v>
-      </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
@@ -3003,9 +3137,6 @@
       <c r="B10" s="2" t="s">
         <v>193</v>
       </c>
-      <c r="C10">
-        <v>5</v>
-      </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
@@ -3030,9 +3161,6 @@
       <c r="B13" s="2" t="s">
         <v>265</v>
       </c>
-      <c r="C13">
-        <v>5</v>
-      </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
@@ -3040,9 +3168,6 @@
       </c>
       <c r="B14" s="2" t="s">
         <v>266</v>
-      </c>
-      <c r="C14">
-        <v>5</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.2">

--- a/urunler.xlsx
+++ b/urunler.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\Githup\portal\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF462902-6312-43E0-9D4F-89635D1F4985}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0789D93-BC41-402B-BEAF-AB6D964B44A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1213,9 +1213,6 @@
       <c r="D2" s="11">
         <v>140.75</v>
       </c>
-      <c r="E2">
-        <v>5</v>
-      </c>
       <c r="F2" s="1">
         <v>5</v>
       </c>
@@ -1237,9 +1234,6 @@
       <c r="D3" s="11">
         <v>162.76</v>
       </c>
-      <c r="E3">
-        <v>5</v>
-      </c>
       <c r="F3" s="1">
         <v>5</v>
       </c>
@@ -1261,9 +1255,6 @@
       <c r="D4" s="2">
         <v>177.95</v>
       </c>
-      <c r="E4">
-        <v>5</v>
-      </c>
       <c r="F4">
         <v>5</v>
       </c>
@@ -1285,9 +1276,6 @@
       <c r="D5" s="2">
         <v>205.06</v>
       </c>
-      <c r="E5">
-        <v>5</v>
-      </c>
       <c r="F5" s="3">
         <v>25</v>
       </c>
@@ -1309,9 +1297,6 @@
       <c r="D6" s="2">
         <v>238.02</v>
       </c>
-      <c r="E6">
-        <v>5</v>
-      </c>
       <c r="F6" s="3">
         <v>5</v>
       </c>
@@ -1333,9 +1318,6 @@
       <c r="D7" s="2">
         <v>81</v>
       </c>
-      <c r="E7">
-        <v>5</v>
-      </c>
       <c r="F7">
         <v>5</v>
       </c>
@@ -1356,9 +1338,6 @@
       <c r="D8" s="2">
         <v>136</v>
       </c>
-      <c r="E8">
-        <v>5</v>
-      </c>
       <c r="F8">
         <v>5</v>
       </c>
@@ -1379,9 +1358,6 @@
       <c r="D9" s="2">
         <v>98</v>
       </c>
-      <c r="E9">
-        <v>5</v>
-      </c>
       <c r="F9">
         <v>5</v>
       </c>
@@ -1402,9 +1378,6 @@
       <c r="D10" s="2">
         <v>116</v>
       </c>
-      <c r="E10">
-        <v>5</v>
-      </c>
       <c r="F10">
         <v>5</v>
       </c>
@@ -1425,9 +1398,6 @@
       <c r="D11" s="2">
         <v>122</v>
       </c>
-      <c r="E11">
-        <v>5</v>
-      </c>
       <c r="F11">
         <v>5</v>
       </c>
@@ -1448,9 +1418,6 @@
       <c r="D12" s="6">
         <v>48.77</v>
       </c>
-      <c r="E12">
-        <v>5</v>
-      </c>
       <c r="F12" s="2">
         <v>2</v>
       </c>
@@ -1471,9 +1438,6 @@
       <c r="D13" s="6">
         <v>7020</v>
       </c>
-      <c r="E13">
-        <v>10</v>
-      </c>
       <c r="F13">
         <v>5</v>
       </c>
@@ -1494,9 +1458,6 @@
       <c r="D14" s="6">
         <v>8255</v>
       </c>
-      <c r="E14">
-        <v>10</v>
-      </c>
       <c r="F14">
         <v>5</v>
       </c>
@@ -1517,9 +1478,6 @@
       <c r="D15" s="6">
         <v>9228.9599999999991</v>
       </c>
-      <c r="E15">
-        <v>10</v>
-      </c>
       <c r="F15">
         <v>5</v>
       </c>
@@ -1540,9 +1498,6 @@
       <c r="D16" s="6">
         <v>10335</v>
       </c>
-      <c r="E16">
-        <v>10</v>
-      </c>
       <c r="F16">
         <v>5</v>
       </c>
@@ -1563,9 +1518,6 @@
       <c r="D17" s="6">
         <v>7620.91</v>
       </c>
-      <c r="E17">
-        <v>10</v>
-      </c>
       <c r="F17">
         <v>5</v>
       </c>
@@ -1586,9 +1538,6 @@
       <c r="D18" s="6">
         <v>2577.54</v>
       </c>
-      <c r="E18">
-        <v>10</v>
-      </c>
       <c r="F18">
         <v>5</v>
       </c>
@@ -1609,9 +1558,6 @@
       <c r="D19" s="6">
         <v>2550.75</v>
       </c>
-      <c r="E19">
-        <v>10</v>
-      </c>
       <c r="F19">
         <v>5</v>
       </c>
@@ -1632,9 +1578,6 @@
       <c r="D20" s="6">
         <v>3226.53</v>
       </c>
-      <c r="E20">
-        <v>10</v>
-      </c>
       <c r="F20">
         <v>5</v>
       </c>
@@ -1655,9 +1598,6 @@
       <c r="D21" s="6">
         <v>3611.43</v>
       </c>
-      <c r="E21">
-        <v>10</v>
-      </c>
       <c r="F21">
         <v>5</v>
       </c>
@@ -1678,9 +1618,6 @@
       <c r="D22" s="6">
         <v>3828.73</v>
       </c>
-      <c r="E22">
-        <v>10</v>
-      </c>
       <c r="F22">
         <v>5</v>
       </c>
@@ -1701,9 +1638,6 @@
       <c r="D23" s="6">
         <v>4020.83</v>
       </c>
-      <c r="E23">
-        <v>10</v>
-      </c>
       <c r="F23">
         <v>5</v>
       </c>
@@ -1724,9 +1658,6 @@
       <c r="D24" s="6">
         <v>4020.91</v>
       </c>
-      <c r="E24">
-        <v>10</v>
-      </c>
       <c r="F24">
         <v>5</v>
       </c>
@@ -1747,9 +1678,6 @@
       <c r="D25" s="6">
         <v>4386.92</v>
       </c>
-      <c r="E25">
-        <v>10</v>
-      </c>
       <c r="F25">
         <v>5</v>
       </c>
@@ -1770,9 +1698,6 @@
       <c r="D26">
         <v>728.72</v>
       </c>
-      <c r="E26">
-        <v>5</v>
-      </c>
       <c r="F26">
         <v>5</v>
       </c>
@@ -1796,9 +1721,6 @@
       <c r="D27">
         <v>474.36</v>
       </c>
-      <c r="E27">
-        <v>5</v>
-      </c>
       <c r="F27">
         <v>5</v>
       </c>
@@ -1822,9 +1744,6 @@
       <c r="D28">
         <v>522.48</v>
       </c>
-      <c r="E28">
-        <v>5</v>
-      </c>
       <c r="F28">
         <v>5</v>
       </c>
@@ -1848,9 +1767,6 @@
       <c r="D29">
         <v>653.98</v>
       </c>
-      <c r="E29">
-        <v>5</v>
-      </c>
       <c r="F29">
         <v>5</v>
       </c>
@@ -1874,9 +1790,6 @@
       <c r="D30">
         <v>172.59</v>
       </c>
-      <c r="E30">
-        <v>5</v>
-      </c>
       <c r="F30">
         <v>24</v>
       </c>
@@ -1900,9 +1813,6 @@
       <c r="D31">
         <v>172.59</v>
       </c>
-      <c r="E31">
-        <v>5</v>
-      </c>
       <c r="G31" s="2" t="s">
         <v>130</v>
       </c>
@@ -1923,9 +1833,6 @@
       <c r="D32">
         <v>21.69</v>
       </c>
-      <c r="E32">
-        <v>5</v>
-      </c>
       <c r="F32">
         <v>108</v>
       </c>
@@ -1949,9 +1856,6 @@
       <c r="D33">
         <v>198.99</v>
       </c>
-      <c r="E33">
-        <v>5</v>
-      </c>
       <c r="F33">
         <v>80</v>
       </c>
@@ -1975,9 +1879,6 @@
       <c r="D34">
         <v>144.99</v>
       </c>
-      <c r="E34">
-        <v>5</v>
-      </c>
       <c r="F34">
         <v>216</v>
       </c>
@@ -2001,9 +1902,6 @@
       <c r="D35">
         <v>165</v>
       </c>
-      <c r="E35">
-        <v>5</v>
-      </c>
       <c r="F35">
         <v>69</v>
       </c>
@@ -2027,9 +1925,6 @@
       <c r="D36">
         <v>179.4</v>
       </c>
-      <c r="E36">
-        <v>5</v>
-      </c>
       <c r="F36">
         <v>61</v>
       </c>
@@ -2053,9 +1948,6 @@
       <c r="D37">
         <v>300</v>
       </c>
-      <c r="E37">
-        <v>5</v>
-      </c>
       <c r="F37">
         <v>76</v>
       </c>
@@ -2079,9 +1971,6 @@
       <c r="D38">
         <v>225</v>
       </c>
-      <c r="E38">
-        <v>5</v>
-      </c>
       <c r="F38">
         <v>47</v>
       </c>
@@ -2105,9 +1994,6 @@
       <c r="D39">
         <v>150</v>
       </c>
-      <c r="E39">
-        <v>5</v>
-      </c>
       <c r="F39">
         <v>16</v>
       </c>
@@ -2131,9 +2017,6 @@
       <c r="D40">
         <v>300</v>
       </c>
-      <c r="E40">
-        <v>5</v>
-      </c>
       <c r="F40">
         <v>21</v>
       </c>
@@ -2157,9 +2040,6 @@
       <c r="D41">
         <v>52.8</v>
       </c>
-      <c r="E41">
-        <v>5</v>
-      </c>
       <c r="F41">
         <v>96</v>
       </c>
@@ -2183,9 +2063,6 @@
       <c r="D42">
         <v>255</v>
       </c>
-      <c r="E42">
-        <v>5</v>
-      </c>
       <c r="F42">
         <v>58</v>
       </c>
@@ -2209,9 +2086,6 @@
       <c r="D43">
         <v>128.4</v>
       </c>
-      <c r="E43">
-        <v>5</v>
-      </c>
       <c r="F43">
         <v>12</v>
       </c>
@@ -2235,9 +2109,6 @@
       <c r="D44">
         <v>127.19999999999999</v>
       </c>
-      <c r="E44">
-        <v>5</v>
-      </c>
       <c r="F44">
         <v>24</v>
       </c>
@@ -2261,9 +2132,6 @@
       <c r="D45">
         <v>180</v>
       </c>
-      <c r="E45">
-        <v>5</v>
-      </c>
       <c r="F45">
         <v>67</v>
       </c>
@@ -2287,9 +2155,6 @@
       <c r="D46">
         <v>202.79999999999998</v>
       </c>
-      <c r="E46">
-        <v>5</v>
-      </c>
       <c r="F46">
         <v>254</v>
       </c>
@@ -2313,9 +2178,6 @@
       <c r="D47">
         <v>127.19999999999999</v>
       </c>
-      <c r="E47">
-        <v>5</v>
-      </c>
       <c r="F47">
         <v>5</v>
       </c>
@@ -2339,9 +2201,6 @@
       <c r="D48">
         <v>150</v>
       </c>
-      <c r="E48">
-        <v>5</v>
-      </c>
       <c r="G48" s="2" t="s">
         <v>147</v>
       </c>
@@ -2362,9 +2221,6 @@
       <c r="D49">
         <v>156</v>
       </c>
-      <c r="E49">
-        <v>5</v>
-      </c>
       <c r="F49">
         <v>46</v>
       </c>
@@ -2388,9 +2244,6 @@
       <c r="D50">
         <v>144</v>
       </c>
-      <c r="E50">
-        <v>5</v>
-      </c>
       <c r="G50" s="2" t="s">
         <v>149</v>
       </c>
@@ -2411,9 +2264,6 @@
       <c r="D51">
         <v>194.4</v>
       </c>
-      <c r="E51">
-        <v>5</v>
-      </c>
       <c r="F51">
         <v>120</v>
       </c>
@@ -2436,9 +2286,6 @@
       </c>
       <c r="D52">
         <v>285</v>
-      </c>
-      <c r="E52">
-        <v>5</v>
       </c>
       <c r="F52">
         <v>39</v>

--- a/urunler.xlsx
+++ b/urunler.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\Githup\portal\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0789D93-BC41-402B-BEAF-AB6D964B44A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6950418-E507-4923-AC69-3C0731FC9374}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2798,6 +2798,9 @@
       <c r="D78">
         <v>467.78399999999999</v>
       </c>
+      <c r="E78">
+        <v>5</v>
+      </c>
       <c r="F78">
         <v>5</v>
       </c>

--- a/urunler.xlsx
+++ b/urunler.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\Githup\portal\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6950418-E507-4923-AC69-3C0731FC9374}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9FBD1D9-5094-4600-ABFA-59121EC46BE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1213,6 +1213,9 @@
       <c r="D2" s="11">
         <v>140.75</v>
       </c>
+      <c r="E2">
+        <v>6</v>
+      </c>
       <c r="F2" s="1">
         <v>5</v>
       </c>
@@ -1234,6 +1237,9 @@
       <c r="D3" s="11">
         <v>162.76</v>
       </c>
+      <c r="E3">
+        <v>6</v>
+      </c>
       <c r="F3" s="1">
         <v>5</v>
       </c>
@@ -1255,6 +1261,9 @@
       <c r="D4" s="2">
         <v>177.95</v>
       </c>
+      <c r="E4">
+        <v>6</v>
+      </c>
       <c r="F4">
         <v>5</v>
       </c>
@@ -1276,6 +1285,9 @@
       <c r="D5" s="2">
         <v>205.06</v>
       </c>
+      <c r="E5">
+        <v>6</v>
+      </c>
       <c r="F5" s="3">
         <v>25</v>
       </c>
@@ -1297,6 +1309,9 @@
       <c r="D6" s="2">
         <v>238.02</v>
       </c>
+      <c r="E6">
+        <v>5</v>
+      </c>
       <c r="F6" s="3">
         <v>5</v>
       </c>
@@ -1318,6 +1333,9 @@
       <c r="D7" s="2">
         <v>81</v>
       </c>
+      <c r="E7">
+        <v>6</v>
+      </c>
       <c r="F7">
         <v>5</v>
       </c>
@@ -1338,6 +1356,9 @@
       <c r="D8" s="2">
         <v>136</v>
       </c>
+      <c r="E8">
+        <v>6</v>
+      </c>
       <c r="F8">
         <v>5</v>
       </c>
@@ -1358,6 +1379,9 @@
       <c r="D9" s="2">
         <v>98</v>
       </c>
+      <c r="E9">
+        <v>6</v>
+      </c>
       <c r="F9">
         <v>5</v>
       </c>
@@ -1378,6 +1402,9 @@
       <c r="D10" s="2">
         <v>116</v>
       </c>
+      <c r="E10">
+        <v>6</v>
+      </c>
       <c r="F10">
         <v>5</v>
       </c>
@@ -1398,6 +1425,9 @@
       <c r="D11" s="2">
         <v>122</v>
       </c>
+      <c r="E11">
+        <v>6</v>
+      </c>
       <c r="F11">
         <v>5</v>
       </c>
@@ -1438,6 +1468,9 @@
       <c r="D13" s="6">
         <v>7020</v>
       </c>
+      <c r="E13">
+        <v>10</v>
+      </c>
       <c r="F13">
         <v>5</v>
       </c>
@@ -1458,6 +1491,9 @@
       <c r="D14" s="6">
         <v>8255</v>
       </c>
+      <c r="E14">
+        <v>10</v>
+      </c>
       <c r="F14">
         <v>5</v>
       </c>
@@ -1478,6 +1514,9 @@
       <c r="D15" s="6">
         <v>9228.9599999999991</v>
       </c>
+      <c r="E15">
+        <v>10</v>
+      </c>
       <c r="F15">
         <v>5</v>
       </c>
@@ -1498,6 +1537,9 @@
       <c r="D16" s="6">
         <v>10335</v>
       </c>
+      <c r="E16">
+        <v>10</v>
+      </c>
       <c r="F16">
         <v>5</v>
       </c>
@@ -1518,6 +1560,9 @@
       <c r="D17" s="6">
         <v>7620.91</v>
       </c>
+      <c r="E17">
+        <v>10</v>
+      </c>
       <c r="F17">
         <v>5</v>
       </c>
@@ -1538,6 +1583,9 @@
       <c r="D18" s="6">
         <v>2577.54</v>
       </c>
+      <c r="E18">
+        <v>10</v>
+      </c>
       <c r="F18">
         <v>5</v>
       </c>
@@ -1558,6 +1606,9 @@
       <c r="D19" s="6">
         <v>2550.75</v>
       </c>
+      <c r="E19">
+        <v>10</v>
+      </c>
       <c r="F19">
         <v>5</v>
       </c>
@@ -1578,6 +1629,9 @@
       <c r="D20" s="6">
         <v>3226.53</v>
       </c>
+      <c r="E20">
+        <v>10</v>
+      </c>
       <c r="F20">
         <v>5</v>
       </c>
@@ -1598,6 +1652,9 @@
       <c r="D21" s="6">
         <v>3611.43</v>
       </c>
+      <c r="E21">
+        <v>10</v>
+      </c>
       <c r="F21">
         <v>5</v>
       </c>
@@ -1618,6 +1675,9 @@
       <c r="D22" s="6">
         <v>3828.73</v>
       </c>
+      <c r="E22">
+        <v>10</v>
+      </c>
       <c r="F22">
         <v>5</v>
       </c>
@@ -1638,6 +1698,9 @@
       <c r="D23" s="6">
         <v>4020.83</v>
       </c>
+      <c r="E23">
+        <v>10</v>
+      </c>
       <c r="F23">
         <v>5</v>
       </c>
@@ -1658,6 +1721,9 @@
       <c r="D24" s="6">
         <v>4020.91</v>
       </c>
+      <c r="E24">
+        <v>10</v>
+      </c>
       <c r="F24">
         <v>5</v>
       </c>
@@ -1677,6 +1743,9 @@
       </c>
       <c r="D25" s="6">
         <v>4386.92</v>
+      </c>
+      <c r="E25">
+        <v>10</v>
       </c>
       <c r="F25">
         <v>5</v>

--- a/urunler.xlsx
+++ b/urunler.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\Githup\portal\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9FBD1D9-5094-4600-ABFA-59121EC46BE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBCAC1F3-3D3B-415E-8D8D-A02A8624C221}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="urunler" sheetId="1" r:id="rId1"/>
@@ -1310,7 +1310,7 @@
         <v>238.02</v>
       </c>
       <c r="E6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F6" s="3">
         <v>5</v>
@@ -2971,7 +2971,7 @@
   <dimension ref="A1:C25"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="16.5703125" customWidth="1"/>
+    <col min="2" max="2" width="24.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.2">
@@ -2992,6 +2992,9 @@
       <c r="B2" t="s">
         <v>29</v>
       </c>
+      <c r="C2">
+        <v>2</v>
+      </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
@@ -3000,6 +3003,9 @@
       <c r="B3" t="s">
         <v>30</v>
       </c>
+      <c r="C3">
+        <v>2</v>
+      </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
@@ -3008,6 +3014,9 @@
       <c r="B4" s="2" t="s">
         <v>187</v>
       </c>
+      <c r="C4">
+        <v>2</v>
+      </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
@@ -3016,6 +3025,9 @@
       <c r="B5" s="2" t="s">
         <v>188</v>
       </c>
+      <c r="C5">
+        <v>2</v>
+      </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
@@ -3024,6 +3036,9 @@
       <c r="B6" s="2" t="s">
         <v>189</v>
       </c>
+      <c r="C6">
+        <v>2</v>
+      </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
@@ -3032,6 +3047,9 @@
       <c r="B7" s="2" t="s">
         <v>190</v>
       </c>
+      <c r="C7">
+        <v>2</v>
+      </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
@@ -3040,6 +3058,9 @@
       <c r="B8" s="2" t="s">
         <v>191</v>
       </c>
+      <c r="C8">
+        <v>2</v>
+      </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
@@ -3048,6 +3069,9 @@
       <c r="B9" s="2" t="s">
         <v>192</v>
       </c>
+      <c r="C9">
+        <v>2</v>
+      </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
@@ -3056,6 +3080,9 @@
       <c r="B10" s="2" t="s">
         <v>193</v>
       </c>
+      <c r="C10">
+        <v>2</v>
+      </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
@@ -3064,6 +3091,9 @@
       <c r="B11" s="2" t="s">
         <v>194</v>
       </c>
+      <c r="C11">
+        <v>2</v>
+      </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
@@ -3072,6 +3102,9 @@
       <c r="B12" s="2" t="s">
         <v>195</v>
       </c>
+      <c r="C12">
+        <v>2</v>
+      </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
@@ -3080,6 +3113,9 @@
       <c r="B13" s="2" t="s">
         <v>265</v>
       </c>
+      <c r="C13">
+        <v>2</v>
+      </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
@@ -3087,6 +3123,9 @@
       </c>
       <c r="B14" s="2" t="s">
         <v>266</v>
+      </c>
+      <c r="C14">
+        <v>2</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.2">

--- a/urunler.xlsx
+++ b/urunler.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\Githup\portal\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBCAC1F3-3D3B-415E-8D8D-A02A8624C221}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F22E103D-A93F-41D3-86CA-84DA2165C761}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="urunler" sheetId="1" r:id="rId1"/>
@@ -923,7 +923,7 @@
     <xf numFmtId="44" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -945,6 +945,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="2"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="2" applyNumberFormat="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="2" applyFill="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1165,7 +1166,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:I83"/>
+  <dimension ref="A1:I84"/>
   <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="57.7109375" customWidth="1"/>
@@ -1213,9 +1214,6 @@
       <c r="D2" s="11">
         <v>140.75</v>
       </c>
-      <c r="E2">
-        <v>6</v>
-      </c>
       <c r="F2" s="1">
         <v>5</v>
       </c>
@@ -1237,9 +1235,6 @@
       <c r="D3" s="11">
         <v>162.76</v>
       </c>
-      <c r="E3">
-        <v>6</v>
-      </c>
       <c r="F3" s="1">
         <v>5</v>
       </c>
@@ -1261,9 +1256,6 @@
       <c r="D4" s="2">
         <v>177.95</v>
       </c>
-      <c r="E4">
-        <v>6</v>
-      </c>
       <c r="F4">
         <v>5</v>
       </c>
@@ -1285,9 +1277,6 @@
       <c r="D5" s="2">
         <v>205.06</v>
       </c>
-      <c r="E5">
-        <v>6</v>
-      </c>
       <c r="F5" s="3">
         <v>25</v>
       </c>
@@ -1309,9 +1298,6 @@
       <c r="D6" s="2">
         <v>238.02</v>
       </c>
-      <c r="E6">
-        <v>6</v>
-      </c>
       <c r="F6" s="3">
         <v>5</v>
       </c>
@@ -1333,9 +1319,6 @@
       <c r="D7" s="2">
         <v>81</v>
       </c>
-      <c r="E7">
-        <v>6</v>
-      </c>
       <c r="F7">
         <v>5</v>
       </c>
@@ -1356,9 +1339,6 @@
       <c r="D8" s="2">
         <v>136</v>
       </c>
-      <c r="E8">
-        <v>6</v>
-      </c>
       <c r="F8">
         <v>5</v>
       </c>
@@ -1379,9 +1359,6 @@
       <c r="D9" s="2">
         <v>98</v>
       </c>
-      <c r="E9">
-        <v>6</v>
-      </c>
       <c r="F9">
         <v>5</v>
       </c>
@@ -1402,9 +1379,6 @@
       <c r="D10" s="2">
         <v>116</v>
       </c>
-      <c r="E10">
-        <v>6</v>
-      </c>
       <c r="F10">
         <v>5</v>
       </c>
@@ -1425,9 +1399,6 @@
       <c r="D11" s="2">
         <v>122</v>
       </c>
-      <c r="E11">
-        <v>6</v>
-      </c>
       <c r="F11">
         <v>5</v>
       </c>
@@ -1469,7 +1440,7 @@
         <v>7020</v>
       </c>
       <c r="E13">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="F13">
         <v>5</v>
@@ -1492,7 +1463,7 @@
         <v>8255</v>
       </c>
       <c r="E14">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="F14">
         <v>5</v>
@@ -1515,7 +1486,7 @@
         <v>9228.9599999999991</v>
       </c>
       <c r="E15">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="F15">
         <v>5</v>
@@ -1538,7 +1509,7 @@
         <v>10335</v>
       </c>
       <c r="E16">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="F16">
         <v>5</v>
@@ -1561,7 +1532,7 @@
         <v>7620.91</v>
       </c>
       <c r="E17">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="F17">
         <v>5</v>
@@ -1584,7 +1555,7 @@
         <v>2577.54</v>
       </c>
       <c r="E18">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="F18">
         <v>5</v>
@@ -1607,7 +1578,7 @@
         <v>2550.75</v>
       </c>
       <c r="E19">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="F19">
         <v>5</v>
@@ -1630,7 +1601,7 @@
         <v>3226.53</v>
       </c>
       <c r="E20">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="F20">
         <v>5</v>
@@ -1653,7 +1624,7 @@
         <v>3611.43</v>
       </c>
       <c r="E21">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="F21">
         <v>5</v>
@@ -1676,7 +1647,7 @@
         <v>3828.73</v>
       </c>
       <c r="E22">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="F22">
         <v>5</v>
@@ -1699,7 +1670,7 @@
         <v>4020.83</v>
       </c>
       <c r="E23">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="F23">
         <v>5</v>
@@ -1722,7 +1693,7 @@
         <v>4020.91</v>
       </c>
       <c r="E24">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="F24">
         <v>5</v>
@@ -1745,7 +1716,7 @@
         <v>4386.92</v>
       </c>
       <c r="E25">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="F25">
         <v>5</v>
@@ -1767,6 +1738,9 @@
       <c r="D26">
         <v>728.72</v>
       </c>
+      <c r="E26">
+        <v>4</v>
+      </c>
       <c r="F26">
         <v>5</v>
       </c>
@@ -1790,6 +1764,9 @@
       <c r="D27">
         <v>474.36</v>
       </c>
+      <c r="E27">
+        <v>4</v>
+      </c>
       <c r="F27">
         <v>5</v>
       </c>
@@ -1813,6 +1790,9 @@
       <c r="D28">
         <v>522.48</v>
       </c>
+      <c r="E28">
+        <v>4</v>
+      </c>
       <c r="F28">
         <v>5</v>
       </c>
@@ -1836,6 +1816,9 @@
       <c r="D29">
         <v>653.98</v>
       </c>
+      <c r="E29">
+        <v>4</v>
+      </c>
       <c r="F29">
         <v>5</v>
       </c>
@@ -1859,6 +1842,9 @@
       <c r="D30">
         <v>172.59</v>
       </c>
+      <c r="E30">
+        <v>4</v>
+      </c>
       <c r="F30">
         <v>24</v>
       </c>
@@ -1882,6 +1868,9 @@
       <c r="D31">
         <v>172.59</v>
       </c>
+      <c r="E31">
+        <v>4</v>
+      </c>
       <c r="G31" s="2" t="s">
         <v>130</v>
       </c>
@@ -1902,6 +1891,9 @@
       <c r="D32">
         <v>21.69</v>
       </c>
+      <c r="E32">
+        <v>4</v>
+      </c>
       <c r="F32">
         <v>108</v>
       </c>
@@ -1925,6 +1917,9 @@
       <c r="D33">
         <v>198.99</v>
       </c>
+      <c r="E33">
+        <v>4</v>
+      </c>
       <c r="F33">
         <v>80</v>
       </c>
@@ -1948,6 +1943,9 @@
       <c r="D34">
         <v>144.99</v>
       </c>
+      <c r="E34">
+        <v>4</v>
+      </c>
       <c r="F34">
         <v>216</v>
       </c>
@@ -1971,6 +1969,9 @@
       <c r="D35">
         <v>165</v>
       </c>
+      <c r="E35">
+        <v>4</v>
+      </c>
       <c r="F35">
         <v>69</v>
       </c>
@@ -1994,6 +1995,9 @@
       <c r="D36">
         <v>179.4</v>
       </c>
+      <c r="E36">
+        <v>4</v>
+      </c>
       <c r="F36">
         <v>61</v>
       </c>
@@ -2017,6 +2021,9 @@
       <c r="D37">
         <v>300</v>
       </c>
+      <c r="E37">
+        <v>4</v>
+      </c>
       <c r="F37">
         <v>76</v>
       </c>
@@ -2040,6 +2047,9 @@
       <c r="D38">
         <v>225</v>
       </c>
+      <c r="E38">
+        <v>4</v>
+      </c>
       <c r="F38">
         <v>47</v>
       </c>
@@ -2063,6 +2073,9 @@
       <c r="D39">
         <v>150</v>
       </c>
+      <c r="E39">
+        <v>4</v>
+      </c>
       <c r="F39">
         <v>16</v>
       </c>
@@ -2086,6 +2099,9 @@
       <c r="D40">
         <v>300</v>
       </c>
+      <c r="E40">
+        <v>4</v>
+      </c>
       <c r="F40">
         <v>21</v>
       </c>
@@ -2109,6 +2125,9 @@
       <c r="D41">
         <v>52.8</v>
       </c>
+      <c r="E41">
+        <v>4</v>
+      </c>
       <c r="F41">
         <v>96</v>
       </c>
@@ -2132,6 +2151,9 @@
       <c r="D42">
         <v>255</v>
       </c>
+      <c r="E42">
+        <v>4</v>
+      </c>
       <c r="F42">
         <v>58</v>
       </c>
@@ -2155,6 +2177,9 @@
       <c r="D43">
         <v>128.4</v>
       </c>
+      <c r="E43">
+        <v>4</v>
+      </c>
       <c r="F43">
         <v>12</v>
       </c>
@@ -2178,6 +2203,9 @@
       <c r="D44">
         <v>127.19999999999999</v>
       </c>
+      <c r="E44">
+        <v>4</v>
+      </c>
       <c r="F44">
         <v>24</v>
       </c>
@@ -2201,6 +2229,9 @@
       <c r="D45">
         <v>180</v>
       </c>
+      <c r="E45">
+        <v>4</v>
+      </c>
       <c r="F45">
         <v>67</v>
       </c>
@@ -2224,6 +2255,9 @@
       <c r="D46">
         <v>202.79999999999998</v>
       </c>
+      <c r="E46">
+        <v>4</v>
+      </c>
       <c r="F46">
         <v>254</v>
       </c>
@@ -2247,6 +2281,9 @@
       <c r="D47">
         <v>127.19999999999999</v>
       </c>
+      <c r="E47">
+        <v>4</v>
+      </c>
       <c r="F47">
         <v>5</v>
       </c>
@@ -2270,6 +2307,9 @@
       <c r="D48">
         <v>150</v>
       </c>
+      <c r="E48">
+        <v>4</v>
+      </c>
       <c r="G48" s="2" t="s">
         <v>147</v>
       </c>
@@ -2290,6 +2330,9 @@
       <c r="D49">
         <v>156</v>
       </c>
+      <c r="E49">
+        <v>4</v>
+      </c>
       <c r="F49">
         <v>46</v>
       </c>
@@ -2313,6 +2356,9 @@
       <c r="D50">
         <v>144</v>
       </c>
+      <c r="E50">
+        <v>4</v>
+      </c>
       <c r="G50" s="2" t="s">
         <v>149</v>
       </c>
@@ -2333,6 +2379,9 @@
       <c r="D51">
         <v>194.4</v>
       </c>
+      <c r="E51">
+        <v>4</v>
+      </c>
       <c r="F51">
         <v>120</v>
       </c>
@@ -2356,6 +2405,9 @@
       <c r="D52">
         <v>285</v>
       </c>
+      <c r="E52">
+        <v>4</v>
+      </c>
       <c r="F52">
         <v>39</v>
       </c>
@@ -2379,7 +2431,9 @@
       <c r="D53" s="10">
         <v>60</v>
       </c>
-      <c r="E53" s="2"/>
+      <c r="E53" s="2">
+        <v>4</v>
+      </c>
       <c r="F53" s="2">
         <v>120</v>
       </c>
@@ -2458,7 +2512,9 @@
       <c r="D59" s="12">
         <v>5583.15</v>
       </c>
-      <c r="E59" s="12"/>
+      <c r="E59" s="12">
+        <v>8</v>
+      </c>
       <c r="F59">
         <v>5</v>
       </c>
@@ -2479,7 +2535,9 @@
       <c r="D60" s="12">
         <v>883.37</v>
       </c>
-      <c r="E60" s="12"/>
+      <c r="E60" s="12">
+        <v>8</v>
+      </c>
       <c r="F60">
         <v>5</v>
       </c>
@@ -2500,7 +2558,9 @@
       <c r="D61" s="12">
         <v>2658.06</v>
       </c>
-      <c r="E61" s="12"/>
+      <c r="E61" s="12">
+        <v>8</v>
+      </c>
       <c r="F61">
         <v>5</v>
       </c>
@@ -2521,7 +2581,9 @@
       <c r="D62" s="12">
         <v>2519.23</v>
       </c>
-      <c r="E62" s="12"/>
+      <c r="E62" s="12">
+        <v>8</v>
+      </c>
       <c r="F62">
         <v>5</v>
       </c>
@@ -2542,7 +2604,9 @@
       <c r="D63" s="12">
         <v>1838.36</v>
       </c>
-      <c r="E63" s="12"/>
+      <c r="E63" s="12">
+        <v>8</v>
+      </c>
       <c r="F63">
         <v>5</v>
       </c>
@@ -2563,7 +2627,9 @@
       <c r="D64" s="12">
         <v>1153.95</v>
       </c>
-      <c r="E64" s="12"/>
+      <c r="E64" s="12">
+        <v>8</v>
+      </c>
       <c r="F64">
         <v>5</v>
       </c>
@@ -2584,7 +2650,9 @@
       <c r="D65" s="12">
         <v>5583.15</v>
       </c>
-      <c r="E65" s="12"/>
+      <c r="E65" s="12">
+        <v>8</v>
+      </c>
       <c r="F65">
         <v>5</v>
       </c>
@@ -2605,7 +2673,9 @@
       <c r="D66" s="12">
         <v>596.87</v>
       </c>
-      <c r="E66" s="12"/>
+      <c r="E66" s="12">
+        <v>8</v>
+      </c>
       <c r="F66">
         <v>5</v>
       </c>
@@ -2626,6 +2696,9 @@
       <c r="D67">
         <v>186.6</v>
       </c>
+      <c r="E67" s="15">
+        <v>4</v>
+      </c>
       <c r="F67">
         <v>5</v>
       </c>
@@ -2649,6 +2722,9 @@
       <c r="D68">
         <v>183.46799999999999</v>
       </c>
+      <c r="E68" s="15">
+        <v>4</v>
+      </c>
       <c r="F68">
         <v>5</v>
       </c>
@@ -2672,6 +2748,9 @@
       <c r="D69">
         <v>150.66</v>
       </c>
+      <c r="E69" s="15">
+        <v>4</v>
+      </c>
       <c r="F69">
         <v>5</v>
       </c>
@@ -2695,6 +2774,9 @@
       <c r="D70">
         <v>187.92</v>
       </c>
+      <c r="E70" s="15">
+        <v>4</v>
+      </c>
       <c r="F70">
         <v>5</v>
       </c>
@@ -2718,6 +2800,9 @@
       <c r="D71">
         <v>411.84</v>
       </c>
+      <c r="E71" s="15">
+        <v>4</v>
+      </c>
       <c r="F71">
         <v>5</v>
       </c>
@@ -2741,6 +2826,9 @@
       <c r="D72">
         <v>499.2</v>
       </c>
+      <c r="E72" s="15">
+        <v>4</v>
+      </c>
       <c r="F72">
         <v>5</v>
       </c>
@@ -2764,6 +2852,9 @@
       <c r="D73">
         <v>450</v>
       </c>
+      <c r="E73" s="15">
+        <v>4</v>
+      </c>
       <c r="F73">
         <v>5</v>
       </c>
@@ -2787,6 +2878,9 @@
       <c r="D74">
         <v>523.5</v>
       </c>
+      <c r="E74" s="15">
+        <v>4</v>
+      </c>
       <c r="F74">
         <v>5</v>
       </c>
@@ -2810,6 +2904,9 @@
       <c r="D75">
         <v>92.04</v>
       </c>
+      <c r="E75" s="15">
+        <v>4</v>
+      </c>
       <c r="F75">
         <v>4</v>
       </c>
@@ -2833,6 +2930,9 @@
       <c r="D76">
         <v>486.28800000000001</v>
       </c>
+      <c r="E76" s="15">
+        <v>4</v>
+      </c>
       <c r="F76">
         <v>5</v>
       </c>
@@ -2850,6 +2950,9 @@
       <c r="D77">
         <v>419.50799999999992</v>
       </c>
+      <c r="E77" s="15">
+        <v>4</v>
+      </c>
       <c r="F77">
         <v>5</v>
       </c>
@@ -2868,7 +2971,7 @@
         <v>467.78399999999999</v>
       </c>
       <c r="E78">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F78">
         <v>5</v>
@@ -2887,6 +2990,9 @@
       <c r="D79">
         <v>487.08000000000004</v>
       </c>
+      <c r="E79" s="15">
+        <v>4</v>
+      </c>
       <c r="F79">
         <v>5</v>
       </c>
@@ -2904,6 +3010,9 @@
       <c r="D80">
         <v>475.99199999999996</v>
       </c>
+      <c r="E80" s="15">
+        <v>4</v>
+      </c>
       <c r="F80">
         <v>5</v>
       </c>
@@ -2921,6 +3030,9 @@
       <c r="D81">
         <v>457.91999999999996</v>
       </c>
+      <c r="E81" s="15">
+        <v>4</v>
+      </c>
       <c r="F81">
         <v>5</v>
       </c>
@@ -2938,6 +3050,9 @@
       <c r="D82">
         <v>529.63200000000006</v>
       </c>
+      <c r="E82" s="15">
+        <v>4</v>
+      </c>
       <c r="F82">
         <v>5</v>
       </c>
@@ -2955,9 +3070,15 @@
       <c r="D83">
         <v>389.95199999999994</v>
       </c>
+      <c r="E83" s="15">
+        <v>4</v>
+      </c>
       <c r="F83">
         <v>5</v>
       </c>
+    </row>
+    <row r="84" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E84" s="15"/>
     </row>
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
@@ -2993,7 +3114,7 @@
         <v>29</v>
       </c>
       <c r="C2">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.2">
@@ -3004,7 +3125,7 @@
         <v>30</v>
       </c>
       <c r="C3">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.2">
@@ -3015,7 +3136,7 @@
         <v>187</v>
       </c>
       <c r="C4">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.2">
@@ -3026,7 +3147,7 @@
         <v>188</v>
       </c>
       <c r="C5">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.2">
@@ -3037,7 +3158,7 @@
         <v>189</v>
       </c>
       <c r="C6">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.2">
@@ -3048,7 +3169,7 @@
         <v>190</v>
       </c>
       <c r="C7">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.2">
@@ -3059,7 +3180,7 @@
         <v>191</v>
       </c>
       <c r="C8">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.2">
@@ -3070,7 +3191,7 @@
         <v>192</v>
       </c>
       <c r="C9">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.2">
@@ -3081,7 +3202,7 @@
         <v>193</v>
       </c>
       <c r="C10">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.2">
@@ -3092,7 +3213,7 @@
         <v>194</v>
       </c>
       <c r="C11">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.2">
@@ -3103,7 +3224,7 @@
         <v>195</v>
       </c>
       <c r="C12">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.2">
@@ -3114,7 +3235,7 @@
         <v>265</v>
       </c>
       <c r="C13">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.2">
@@ -3125,7 +3246,7 @@
         <v>266</v>
       </c>
       <c r="C14">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.2">

--- a/urunler.xlsx
+++ b/urunler.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\Githup\portal\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F22E103D-A93F-41D3-86CA-84DA2165C761}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{405D3F40-65A3-4558-AADF-417CC987705A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -923,7 +923,7 @@
     <xf numFmtId="44" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -945,7 +945,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="2"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="2" applyNumberFormat="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="2" applyFill="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1738,9 +1737,6 @@
       <c r="D26">
         <v>728.72</v>
       </c>
-      <c r="E26">
-        <v>4</v>
-      </c>
       <c r="F26">
         <v>5</v>
       </c>
@@ -1764,9 +1760,6 @@
       <c r="D27">
         <v>474.36</v>
       </c>
-      <c r="E27">
-        <v>4</v>
-      </c>
       <c r="F27">
         <v>5</v>
       </c>
@@ -1790,9 +1783,6 @@
       <c r="D28">
         <v>522.48</v>
       </c>
-      <c r="E28">
-        <v>4</v>
-      </c>
       <c r="F28">
         <v>5</v>
       </c>
@@ -1816,9 +1806,6 @@
       <c r="D29">
         <v>653.98</v>
       </c>
-      <c r="E29">
-        <v>4</v>
-      </c>
       <c r="F29">
         <v>5</v>
       </c>
@@ -1842,9 +1829,6 @@
       <c r="D30">
         <v>172.59</v>
       </c>
-      <c r="E30">
-        <v>4</v>
-      </c>
       <c r="F30">
         <v>24</v>
       </c>
@@ -1868,9 +1852,6 @@
       <c r="D31">
         <v>172.59</v>
       </c>
-      <c r="E31">
-        <v>4</v>
-      </c>
       <c r="G31" s="2" t="s">
         <v>130</v>
       </c>
@@ -1891,9 +1872,6 @@
       <c r="D32">
         <v>21.69</v>
       </c>
-      <c r="E32">
-        <v>4</v>
-      </c>
       <c r="F32">
         <v>108</v>
       </c>
@@ -1917,9 +1895,6 @@
       <c r="D33">
         <v>198.99</v>
       </c>
-      <c r="E33">
-        <v>4</v>
-      </c>
       <c r="F33">
         <v>80</v>
       </c>
@@ -1943,9 +1918,6 @@
       <c r="D34">
         <v>144.99</v>
       </c>
-      <c r="E34">
-        <v>4</v>
-      </c>
       <c r="F34">
         <v>216</v>
       </c>
@@ -1969,9 +1941,6 @@
       <c r="D35">
         <v>165</v>
       </c>
-      <c r="E35">
-        <v>4</v>
-      </c>
       <c r="F35">
         <v>69</v>
       </c>
@@ -1995,9 +1964,6 @@
       <c r="D36">
         <v>179.4</v>
       </c>
-      <c r="E36">
-        <v>4</v>
-      </c>
       <c r="F36">
         <v>61</v>
       </c>
@@ -2021,9 +1987,6 @@
       <c r="D37">
         <v>300</v>
       </c>
-      <c r="E37">
-        <v>4</v>
-      </c>
       <c r="F37">
         <v>76</v>
       </c>
@@ -2047,9 +2010,6 @@
       <c r="D38">
         <v>225</v>
       </c>
-      <c r="E38">
-        <v>4</v>
-      </c>
       <c r="F38">
         <v>47</v>
       </c>
@@ -2073,9 +2033,6 @@
       <c r="D39">
         <v>150</v>
       </c>
-      <c r="E39">
-        <v>4</v>
-      </c>
       <c r="F39">
         <v>16</v>
       </c>
@@ -2099,9 +2056,6 @@
       <c r="D40">
         <v>300</v>
       </c>
-      <c r="E40">
-        <v>4</v>
-      </c>
       <c r="F40">
         <v>21</v>
       </c>
@@ -2125,9 +2079,6 @@
       <c r="D41">
         <v>52.8</v>
       </c>
-      <c r="E41">
-        <v>4</v>
-      </c>
       <c r="F41">
         <v>96</v>
       </c>
@@ -2151,9 +2102,6 @@
       <c r="D42">
         <v>255</v>
       </c>
-      <c r="E42">
-        <v>4</v>
-      </c>
       <c r="F42">
         <v>58</v>
       </c>
@@ -2177,9 +2125,6 @@
       <c r="D43">
         <v>128.4</v>
       </c>
-      <c r="E43">
-        <v>4</v>
-      </c>
       <c r="F43">
         <v>12</v>
       </c>
@@ -2203,9 +2148,6 @@
       <c r="D44">
         <v>127.19999999999999</v>
       </c>
-      <c r="E44">
-        <v>4</v>
-      </c>
       <c r="F44">
         <v>24</v>
       </c>
@@ -2229,9 +2171,6 @@
       <c r="D45">
         <v>180</v>
       </c>
-      <c r="E45">
-        <v>4</v>
-      </c>
       <c r="F45">
         <v>67</v>
       </c>
@@ -2255,9 +2194,6 @@
       <c r="D46">
         <v>202.79999999999998</v>
       </c>
-      <c r="E46">
-        <v>4</v>
-      </c>
       <c r="F46">
         <v>254</v>
       </c>
@@ -2281,9 +2217,6 @@
       <c r="D47">
         <v>127.19999999999999</v>
       </c>
-      <c r="E47">
-        <v>4</v>
-      </c>
       <c r="F47">
         <v>5</v>
       </c>
@@ -2307,9 +2240,6 @@
       <c r="D48">
         <v>150</v>
       </c>
-      <c r="E48">
-        <v>4</v>
-      </c>
       <c r="G48" s="2" t="s">
         <v>147</v>
       </c>
@@ -2330,9 +2260,6 @@
       <c r="D49">
         <v>156</v>
       </c>
-      <c r="E49">
-        <v>4</v>
-      </c>
       <c r="F49">
         <v>46</v>
       </c>
@@ -2356,9 +2283,6 @@
       <c r="D50">
         <v>144</v>
       </c>
-      <c r="E50">
-        <v>4</v>
-      </c>
       <c r="G50" s="2" t="s">
         <v>149</v>
       </c>
@@ -2379,9 +2303,6 @@
       <c r="D51">
         <v>194.4</v>
       </c>
-      <c r="E51">
-        <v>4</v>
-      </c>
       <c r="F51">
         <v>120</v>
       </c>
@@ -2405,9 +2326,6 @@
       <c r="D52">
         <v>285</v>
       </c>
-      <c r="E52">
-        <v>4</v>
-      </c>
       <c r="F52">
         <v>39</v>
       </c>
@@ -2431,9 +2349,7 @@
       <c r="D53" s="10">
         <v>60</v>
       </c>
-      <c r="E53" s="2">
-        <v>4</v>
-      </c>
+      <c r="E53" s="2"/>
       <c r="F53" s="2">
         <v>120</v>
       </c>
@@ -2696,9 +2612,7 @@
       <c r="D67">
         <v>186.6</v>
       </c>
-      <c r="E67" s="15">
-        <v>4</v>
-      </c>
+      <c r="E67" s="12"/>
       <c r="F67">
         <v>5</v>
       </c>
@@ -2722,9 +2636,7 @@
       <c r="D68">
         <v>183.46799999999999</v>
       </c>
-      <c r="E68" s="15">
-        <v>4</v>
-      </c>
+      <c r="E68" s="12"/>
       <c r="F68">
         <v>5</v>
       </c>
@@ -2748,9 +2660,7 @@
       <c r="D69">
         <v>150.66</v>
       </c>
-      <c r="E69" s="15">
-        <v>4</v>
-      </c>
+      <c r="E69" s="12"/>
       <c r="F69">
         <v>5</v>
       </c>
@@ -2774,9 +2684,7 @@
       <c r="D70">
         <v>187.92</v>
       </c>
-      <c r="E70" s="15">
-        <v>4</v>
-      </c>
+      <c r="E70" s="12"/>
       <c r="F70">
         <v>5</v>
       </c>
@@ -2800,9 +2708,7 @@
       <c r="D71">
         <v>411.84</v>
       </c>
-      <c r="E71" s="15">
-        <v>4</v>
-      </c>
+      <c r="E71" s="12"/>
       <c r="F71">
         <v>5</v>
       </c>
@@ -2826,9 +2732,7 @@
       <c r="D72">
         <v>499.2</v>
       </c>
-      <c r="E72" s="15">
-        <v>4</v>
-      </c>
+      <c r="E72" s="12"/>
       <c r="F72">
         <v>5</v>
       </c>
@@ -2852,9 +2756,7 @@
       <c r="D73">
         <v>450</v>
       </c>
-      <c r="E73" s="15">
-        <v>4</v>
-      </c>
+      <c r="E73" s="12"/>
       <c r="F73">
         <v>5</v>
       </c>
@@ -2878,9 +2780,7 @@
       <c r="D74">
         <v>523.5</v>
       </c>
-      <c r="E74" s="15">
-        <v>4</v>
-      </c>
+      <c r="E74" s="12"/>
       <c r="F74">
         <v>5</v>
       </c>
@@ -2904,9 +2804,7 @@
       <c r="D75">
         <v>92.04</v>
       </c>
-      <c r="E75" s="15">
-        <v>4</v>
-      </c>
+      <c r="E75" s="12"/>
       <c r="F75">
         <v>4</v>
       </c>
@@ -2930,9 +2828,7 @@
       <c r="D76">
         <v>486.28800000000001</v>
       </c>
-      <c r="E76" s="15">
-        <v>4</v>
-      </c>
+      <c r="E76" s="12"/>
       <c r="F76">
         <v>5</v>
       </c>
@@ -2950,9 +2846,7 @@
       <c r="D77">
         <v>419.50799999999992</v>
       </c>
-      <c r="E77" s="15">
-        <v>4</v>
-      </c>
+      <c r="E77" s="12"/>
       <c r="F77">
         <v>5</v>
       </c>
@@ -2970,9 +2864,6 @@
       <c r="D78">
         <v>467.78399999999999</v>
       </c>
-      <c r="E78">
-        <v>4</v>
-      </c>
       <c r="F78">
         <v>5</v>
       </c>
@@ -2990,9 +2881,7 @@
       <c r="D79">
         <v>487.08000000000004</v>
       </c>
-      <c r="E79" s="15">
-        <v>4</v>
-      </c>
+      <c r="E79" s="12"/>
       <c r="F79">
         <v>5</v>
       </c>
@@ -3010,9 +2899,7 @@
       <c r="D80">
         <v>475.99199999999996</v>
       </c>
-      <c r="E80" s="15">
-        <v>4</v>
-      </c>
+      <c r="E80" s="12"/>
       <c r="F80">
         <v>5</v>
       </c>
@@ -3030,9 +2917,7 @@
       <c r="D81">
         <v>457.91999999999996</v>
       </c>
-      <c r="E81" s="15">
-        <v>4</v>
-      </c>
+      <c r="E81" s="12"/>
       <c r="F81">
         <v>5</v>
       </c>
@@ -3050,9 +2935,7 @@
       <c r="D82">
         <v>529.63200000000006</v>
       </c>
-      <c r="E82" s="15">
-        <v>4</v>
-      </c>
+      <c r="E82" s="12"/>
       <c r="F82">
         <v>5</v>
       </c>
@@ -3070,15 +2953,13 @@
       <c r="D83">
         <v>389.95199999999994</v>
       </c>
-      <c r="E83" s="15">
-        <v>4</v>
-      </c>
+      <c r="E83" s="12"/>
       <c r="F83">
         <v>5</v>
       </c>
     </row>
     <row r="84" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="E84" s="15"/>
+      <c r="E84" s="12"/>
     </row>
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>

--- a/urunler.xlsx
+++ b/urunler.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\Githup\portal\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{405D3F40-65A3-4558-AADF-417CC987705A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4FADED50-984F-4F3F-8D83-3F24396BB65D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1211,7 +1211,7 @@
         <v>45</v>
       </c>
       <c r="D2" s="11">
-        <v>140.75</v>
+        <v>141.49440000000001</v>
       </c>
       <c r="F2" s="1">
         <v>5</v>
@@ -1316,7 +1316,7 @@
         <v>45</v>
       </c>
       <c r="D7" s="2">
-        <v>81</v>
+        <v>79.73</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -1336,7 +1336,7 @@
         <v>45</v>
       </c>
       <c r="D8" s="2">
-        <v>136</v>
+        <v>126.4118</v>
       </c>
       <c r="F8">
         <v>5</v>
@@ -1356,7 +1356,7 @@
         <v>45</v>
       </c>
       <c r="D9" s="2">
-        <v>98</v>
+        <v>96.611999999999995</v>
       </c>
       <c r="F9">
         <v>5</v>
@@ -1376,7 +1376,7 @@
         <v>45</v>
       </c>
       <c r="D10" s="2">
-        <v>116</v>
+        <v>110.11799999999999</v>
       </c>
       <c r="F10">
         <v>5</v>
@@ -1396,7 +1396,7 @@
         <v>45</v>
       </c>
       <c r="D11" s="2">
-        <v>122</v>
+        <v>120.3432</v>
       </c>
       <c r="F11">
         <v>5</v>

--- a/urunler.xlsx
+++ b/urunler.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\Githup\portal\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4FADED50-984F-4F3F-8D83-3F24396BB65D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70FED280-B2BB-4BD4-86AA-4AC2B2619E10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1515" yWindow="1515" windowWidth="18870" windowHeight="9360" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="urunler" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="348" uniqueCount="267">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="349" uniqueCount="268">
   <si>
     <t>urun_no</t>
   </si>
@@ -835,6 +835,9 @@
   </si>
   <si>
     <t>BAŞKENT OTOMOTİV</t>
+  </si>
+  <si>
+    <t>MURAT DÖNMEZ</t>
   </si>
 </sst>
 </file>
@@ -923,7 +926,7 @@
     <xf numFmtId="44" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -945,6 +948,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="2"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="2" applyNumberFormat="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3134,6 +3138,9 @@
       <c r="A15" t="s">
         <v>18</v>
       </c>
+      <c r="B15" s="15" t="s">
+        <v>267</v>
+      </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A16" t="s">

--- a/urunler.xlsx
+++ b/urunler.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\Githup\portal\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70FED280-B2BB-4BD4-86AA-4AC2B2619E10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B06ABE60-7A98-4A64-8929-BC01439F261B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1515" yWindow="1515" windowWidth="18870" windowHeight="9360" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="349" uniqueCount="268">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="346" uniqueCount="270">
   <si>
     <t>urun_no</t>
   </si>
@@ -838,6 +838,12 @@
   </si>
   <si>
     <t>MURAT DÖNMEZ</t>
+  </si>
+  <si>
+    <t>8090.PNG</t>
+  </si>
+  <si>
+    <t>8091.PNG</t>
   </si>
 </sst>
 </file>
@@ -1430,8 +1436,8 @@
       </c>
     </row>
     <row r="13" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" t="s">
-        <v>56</v>
+      <c r="A13" s="5">
+        <v>7589</v>
       </c>
       <c r="B13" t="s">
         <v>65</v>
@@ -1522,8 +1528,8 @@
       </c>
     </row>
     <row r="17" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" t="s">
-        <v>57</v>
+      <c r="A17" s="5">
+        <v>8091</v>
       </c>
       <c r="B17" t="s">
         <v>69</v>
@@ -1540,8 +1546,8 @@
       <c r="F17">
         <v>5</v>
       </c>
-      <c r="G17" s="2" t="s">
-        <v>80</v>
+      <c r="G17" s="15" t="s">
+        <v>269</v>
       </c>
     </row>
     <row r="18" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -1637,8 +1643,8 @@
       </c>
     </row>
     <row r="22" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" t="s">
-        <v>57</v>
+      <c r="A22" s="5">
+        <v>8090</v>
       </c>
       <c r="B22" t="s">
         <v>74</v>
@@ -1655,8 +1661,8 @@
       <c r="F22">
         <v>5</v>
       </c>
-      <c r="G22" s="2" t="s">
-        <v>80</v>
+      <c r="G22" s="15" t="s">
+        <v>268</v>
       </c>
     </row>
     <row r="23" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -3043,7 +3049,7 @@
         <v>189</v>
       </c>
       <c r="C6">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.2">
@@ -3087,7 +3093,7 @@
         <v>193</v>
       </c>
       <c r="C10">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.2">
